--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R2" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,32 +806,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R3" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +882,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,26 +895,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132811968</v>
+        <v>132811929</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521278</v>
+        <v>521300</v>
       </c>
       <c r="R18" t="n">
-        <v>7009051</v>
+        <v>7009023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,6 +2731,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad tallved i tallskog.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2758,12 +2763,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2781,10 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811970</v>
+        <v>132811902</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,21 +2797,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521326</v>
+        <v>521234</v>
       </c>
       <c r="R19" t="n">
-        <v>7008987</v>
+        <v>7008999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2869,7 +2874,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2884,12 +2889,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2907,65 +2912,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811944</v>
+        <v>132811968</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521377</v>
+        <v>521278</v>
       </c>
       <c r="R20" t="n">
-        <v>7009007</v>
+        <v>7009051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3000,11 +2988,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3018,6 +3001,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3035,10 +3038,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811929</v>
+        <v>132811970</v>
       </c>
       <c r="B21" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3046,21 +3049,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3073,10 +3076,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521300</v>
+        <v>521326</v>
       </c>
       <c r="R21" t="n">
-        <v>7009023</v>
+        <v>7008987</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3111,11 +3114,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad tallved i tallskog.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3143,12 +3141,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,48 +3164,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811902</v>
+        <v>132811944</v>
       </c>
       <c r="B22" t="n">
-        <v>79923</v>
+        <v>99130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521234</v>
+        <v>521377</v>
       </c>
       <c r="R22" t="n">
-        <v>7008999</v>
+        <v>7009007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3242,6 +3257,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3254,27 +3274,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3942,42 +3942,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132811984</v>
+        <v>132811965</v>
       </c>
       <c r="B28" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3985,10 +3980,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521469</v>
+        <v>521397</v>
       </c>
       <c r="R28" t="n">
-        <v>7008936</v>
+        <v>7008961</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4035,7 +4030,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4053,37 +4068,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132811965</v>
+        <v>132811984</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4091,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521397</v>
+        <v>521469</v>
       </c>
       <c r="R29" t="n">
-        <v>7008961</v>
+        <v>7008936</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4141,27 +4161,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4179,65 +4179,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811949</v>
+        <v>132811924</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>80466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521297</v>
+        <v>521413</v>
       </c>
       <c r="R30" t="n">
-        <v>7009058</v>
+        <v>7008949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4272,11 +4255,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4289,7 +4267,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4307,42 +4285,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132811988</v>
+        <v>132811957</v>
       </c>
       <c r="B31" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4350,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521434</v>
+        <v>521417</v>
       </c>
       <c r="R31" t="n">
-        <v>7008976</v>
+        <v>7008923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4388,11 +4361,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4405,7 +4373,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4542,48 +4530,65 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811957</v>
+        <v>132811949</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521417</v>
+        <v>521297</v>
       </c>
       <c r="R33" t="n">
-        <v>7008923</v>
+        <v>7009058</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4618,6 +4623,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4630,27 +4640,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4668,10 +4658,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811924</v>
+        <v>132811988</v>
       </c>
       <c r="B34" t="n">
-        <v>80466</v>
+        <v>101338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4679,26 +4669,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4706,10 +4701,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521413</v>
+        <v>521434</v>
       </c>
       <c r="R34" t="n">
-        <v>7008949</v>
+        <v>7008976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,6 +4739,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5095,32 +5095,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132840125</v>
+        <v>132840095</v>
       </c>
       <c r="B38" t="n">
-        <v>92192</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521309</v>
+        <v>521362</v>
       </c>
       <c r="R38" t="n">
-        <v>7008931</v>
+        <v>7009022</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5202,32 +5202,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132840095</v>
+        <v>132840125</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>92192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521362</v>
+        <v>521309</v>
       </c>
       <c r="R39" t="n">
-        <v>7009022</v>
+        <v>7008931</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5416,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132840111</v>
+        <v>132840103</v>
       </c>
       <c r="B41" t="n">
-        <v>78345</v>
+        <v>83315</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521478</v>
+        <v>521403</v>
       </c>
       <c r="R41" t="n">
-        <v>7008952</v>
+        <v>7008996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840103</v>
+        <v>132840108</v>
       </c>
       <c r="B42" t="n">
-        <v>83315</v>
+        <v>91918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521403</v>
+        <v>521417</v>
       </c>
       <c r="R42" t="n">
-        <v>7008996</v>
+        <v>7008986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132840108</v>
+        <v>132840111</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>78345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521417</v>
+        <v>521478</v>
       </c>
       <c r="R43" t="n">
-        <v>7008986</v>
+        <v>7008952</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132840092</v>
+        <v>132840100</v>
       </c>
       <c r="B52" t="n">
-        <v>91971</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521309</v>
+        <v>521390</v>
       </c>
       <c r="R52" t="n">
-        <v>7008998</v>
+        <v>7009025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,21 +6699,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6730,10 +6715,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132840100</v>
+        <v>132840092</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>91971</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6741,21 +6726,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6765,10 +6750,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521390</v>
+        <v>521309</v>
       </c>
       <c r="R53" t="n">
-        <v>7009025</v>
+        <v>7008998</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6800,7 +6785,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6810,7 +6795,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6821,6 +6806,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7606,10 +7606,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132840098</v>
+        <v>132840096</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521390</v>
+        <v>521376</v>
       </c>
       <c r="R61" t="n">
-        <v>7009005</v>
+        <v>7009026</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7713,10 +7713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132840096</v>
+        <v>132840098</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7724,21 +7724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521376</v>
+        <v>521390</v>
       </c>
       <c r="R62" t="n">
-        <v>7009026</v>
+        <v>7009005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7960,32 +7960,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934698</v>
+        <v>132934683</v>
       </c>
       <c r="B64" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521353</v>
+        <v>521412</v>
       </c>
       <c r="R64" t="n">
-        <v>7008984</v>
+        <v>7008950</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8057,10 +8057,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934638</v>
+        <v>132934698</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8068,21 +8068,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521314</v>
+        <v>521353</v>
       </c>
       <c r="R65" t="n">
-        <v>7009064</v>
+        <v>7008984</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8154,10 +8154,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934540</v>
+        <v>132934638</v>
       </c>
       <c r="B66" t="n">
-        <v>79090</v>
+        <v>80438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8165,34 +8165,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521347</v>
+        <v>521314</v>
       </c>
       <c r="R66" t="n">
-        <v>7008990</v>
+        <v>7009064</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8251,10 +8251,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934556</v>
+        <v>132934540</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521357</v>
+        <v>521347</v>
       </c>
       <c r="R67" t="n">
-        <v>7008968</v>
+        <v>7008990</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,11 +8322,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8353,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934639</v>
+        <v>132934556</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8364,34 +8359,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521297</v>
+        <v>521357</v>
       </c>
       <c r="R68" t="n">
-        <v>7009054</v>
+        <v>7008968</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8424,6 +8419,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8450,32 +8450,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934683</v>
+        <v>132934639</v>
       </c>
       <c r="B69" t="n">
-        <v>92092</v>
+        <v>80438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521412</v>
+        <v>521297</v>
       </c>
       <c r="R69" t="n">
-        <v>7008950</v>
+        <v>7009054</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8547,32 +8547,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934632</v>
+        <v>132934654</v>
       </c>
       <c r="B70" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521385</v>
+        <v>521338</v>
       </c>
       <c r="R70" t="n">
-        <v>7009021</v>
+        <v>7009053</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8644,32 +8644,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934654</v>
+        <v>132934632</v>
       </c>
       <c r="B71" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8679,10 +8679,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521338</v>
+        <v>521385</v>
       </c>
       <c r="R71" t="n">
-        <v>7009053</v>
+        <v>7009021</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8741,32 +8741,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934713</v>
+        <v>132934656</v>
       </c>
       <c r="B72" t="n">
-        <v>92192</v>
+        <v>80398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>65</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521238</v>
+        <v>521300</v>
       </c>
       <c r="R72" t="n">
-        <v>7008997</v>
+        <v>7009071</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8935,32 +8935,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934656</v>
+        <v>132934713</v>
       </c>
       <c r="B74" t="n">
-        <v>80398</v>
+        <v>92192</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>65</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521300</v>
+        <v>521238</v>
       </c>
       <c r="R74" t="n">
-        <v>7009071</v>
+        <v>7008997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9614,32 +9614,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934706</v>
+        <v>132934688</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521426</v>
+        <v>521335</v>
       </c>
       <c r="R81" t="n">
-        <v>7008976</v>
+        <v>7009020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9711,10 +9711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934707</v>
+        <v>132934563</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>97370</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521289</v>
+        <v>521415</v>
       </c>
       <c r="R82" t="n">
-        <v>7008957</v>
+        <v>7008980</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934721</v>
+        <v>132934706</v>
       </c>
       <c r="B83" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521464</v>
+        <v>521426</v>
       </c>
       <c r="R83" t="n">
-        <v>7008859</v>
+        <v>7008976</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934688</v>
+        <v>132934707</v>
       </c>
       <c r="B84" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521335</v>
+        <v>521289</v>
       </c>
       <c r="R84" t="n">
-        <v>7009020</v>
+        <v>7008957</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9970,12 +9970,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10002,32 +10002,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934624</v>
+        <v>132934721</v>
       </c>
       <c r="B85" t="n">
-        <v>79091</v>
+        <v>93206</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521279</v>
+        <v>521464</v>
       </c>
       <c r="R85" t="n">
-        <v>7008952</v>
+        <v>7008859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10099,7 +10099,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934623</v>
+        <v>132934624</v>
       </c>
       <c r="B86" t="n">
         <v>79091</v>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521457</v>
+        <v>521279</v>
       </c>
       <c r="R86" t="n">
-        <v>7008866</v>
+        <v>7008952</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934563</v>
+        <v>132934623</v>
       </c>
       <c r="B87" t="n">
-        <v>97370</v>
+        <v>79091</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10207,21 +10207,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521415</v>
+        <v>521457</v>
       </c>
       <c r="R87" t="n">
-        <v>7008980</v>
+        <v>7008866</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10584,32 +10584,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934661</v>
+        <v>132934668</v>
       </c>
       <c r="B91" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521456</v>
+        <v>521460</v>
       </c>
       <c r="R91" t="n">
-        <v>7008920</v>
+        <v>7008862</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10655,6 +10655,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,32 +10686,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934705</v>
+        <v>132934657</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10716,10 +10721,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521416</v>
+        <v>521311</v>
       </c>
       <c r="R92" t="n">
-        <v>7008940</v>
+        <v>7009049</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10746,12 +10751,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10778,10 +10783,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934699</v>
+        <v>132934508</v>
       </c>
       <c r="B93" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10789,34 +10794,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521371</v>
+        <v>521332</v>
       </c>
       <c r="R93" t="n">
-        <v>7009040</v>
+        <v>7009041</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10875,32 +10880,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934723</v>
+        <v>132934711</v>
       </c>
       <c r="B94" t="n">
-        <v>93206</v>
+        <v>92192</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10910,10 +10915,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521262</v>
+        <v>521269</v>
       </c>
       <c r="R94" t="n">
-        <v>7009041</v>
+        <v>7008900</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10972,10 +10977,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934508</v>
+        <v>132934661</v>
       </c>
       <c r="B95" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10983,34 +10988,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521332</v>
+        <v>521456</v>
       </c>
       <c r="R95" t="n">
-        <v>7009041</v>
+        <v>7008920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11037,12 +11042,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11069,32 +11074,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934668</v>
+        <v>132934705</v>
       </c>
       <c r="B96" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11104,10 +11109,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521460</v>
+        <v>521416</v>
       </c>
       <c r="R96" t="n">
-        <v>7008862</v>
+        <v>7008940</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11140,11 +11145,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11171,32 +11171,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934657</v>
+        <v>132934699</v>
       </c>
       <c r="B97" t="n">
-        <v>80398</v>
+        <v>79333</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521311</v>
+        <v>521371</v>
       </c>
       <c r="R97" t="n">
-        <v>7009049</v>
+        <v>7009040</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11268,32 +11268,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934711</v>
+        <v>132934723</v>
       </c>
       <c r="B98" t="n">
-        <v>92192</v>
+        <v>93206</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521269</v>
+        <v>521262</v>
       </c>
       <c r="R98" t="n">
-        <v>7008900</v>
+        <v>7009041</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11365,32 +11365,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934603</v>
+        <v>132934685</v>
       </c>
       <c r="B99" t="n">
-        <v>80342</v>
+        <v>92092</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521339</v>
+        <v>521278</v>
       </c>
       <c r="R99" t="n">
-        <v>7009060</v>
+        <v>7008985</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11462,45 +11462,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934685</v>
+        <v>132934505</v>
       </c>
       <c r="B100" t="n">
-        <v>92092</v>
+        <v>97370</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521278</v>
+        <v>521304</v>
       </c>
       <c r="R100" t="n">
-        <v>7008985</v>
+        <v>7009055</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11559,45 +11559,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934505</v>
+        <v>132934603</v>
       </c>
       <c r="B101" t="n">
-        <v>97370</v>
+        <v>80342</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521304</v>
+        <v>521339</v>
       </c>
       <c r="R101" t="n">
-        <v>7009055</v>
+        <v>7009060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11656,7 +11656,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934621</v>
+        <v>132934520</v>
       </c>
       <c r="B102" t="n">
         <v>79091</v>
@@ -11687,14 +11687,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521284</v>
+        <v>521367</v>
       </c>
       <c r="R102" t="n">
-        <v>7008883</v>
+        <v>7008928</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11721,12 +11721,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11753,10 +11753,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934580</v>
+        <v>132934621</v>
       </c>
       <c r="B103" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11764,21 +11764,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521256</v>
+        <v>521284</v>
       </c>
       <c r="R103" t="n">
-        <v>7008979</v>
+        <v>7008883</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11850,10 +11850,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934520</v>
+        <v>132934580</v>
       </c>
       <c r="B104" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11861,34 +11861,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521367</v>
+        <v>521256</v>
       </c>
       <c r="R104" t="n">
-        <v>7008928</v>
+        <v>7008979</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11915,12 +11915,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12243,10 +12243,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132934637</v>
+        <v>132934715</v>
       </c>
       <c r="B108" t="n">
-        <v>80438</v>
+        <v>78999</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12254,21 +12254,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>521330</v>
+        <v>521370</v>
       </c>
       <c r="R108" t="n">
-        <v>7009056</v>
+        <v>7008865</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12308,17 +12308,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12345,32 +12340,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934715</v>
+        <v>132934712</v>
       </c>
       <c r="B109" t="n">
-        <v>78999</v>
+        <v>92192</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12380,10 +12375,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521370</v>
+        <v>521471</v>
       </c>
       <c r="R109" t="n">
-        <v>7008865</v>
+        <v>7008872</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12442,32 +12437,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934712</v>
+        <v>132934637</v>
       </c>
       <c r="B110" t="n">
-        <v>92192</v>
+        <v>80438</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12477,10 +12472,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521471</v>
+        <v>521330</v>
       </c>
       <c r="R110" t="n">
-        <v>7008872</v>
+        <v>7009056</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12507,12 +12502,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12539,32 +12539,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934645</v>
+        <v>132934651</v>
       </c>
       <c r="B111" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521343</v>
+        <v>521370</v>
       </c>
       <c r="R111" t="n">
-        <v>7009058</v>
+        <v>7009038</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12604,17 +12604,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12641,32 +12636,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934651</v>
+        <v>132934645</v>
       </c>
       <c r="B112" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12676,10 +12671,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521370</v>
+        <v>521343</v>
       </c>
       <c r="R112" t="n">
-        <v>7009038</v>
+        <v>7009058</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12706,12 +12701,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12835,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934518</v>
+        <v>132934584</v>
       </c>
       <c r="B114" t="n">
-        <v>79091</v>
+        <v>91918</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12846,34 +12846,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521253</v>
+        <v>521471</v>
       </c>
       <c r="R114" t="n">
-        <v>7009010</v>
+        <v>7008946</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12932,32 +12932,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934732</v>
+        <v>132934689</v>
       </c>
       <c r="B115" t="n">
-        <v>78736</v>
+        <v>92092</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521236</v>
+        <v>521289</v>
       </c>
       <c r="R115" t="n">
-        <v>7009004</v>
+        <v>7009060</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,12 +12997,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934584</v>
+        <v>132934732</v>
       </c>
       <c r="B116" t="n">
-        <v>91918</v>
+        <v>78736</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521471</v>
+        <v>521236</v>
       </c>
       <c r="R116" t="n">
-        <v>7008946</v>
+        <v>7009004</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13126,45 +13126,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934689</v>
+        <v>132934518</v>
       </c>
       <c r="B117" t="n">
-        <v>92092</v>
+        <v>79091</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521289</v>
+        <v>521253</v>
       </c>
       <c r="R117" t="n">
-        <v>7009060</v>
+        <v>7009010</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14193,32 +14193,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934687</v>
+        <v>132934718</v>
       </c>
       <c r="B128" t="n">
-        <v>92092</v>
+        <v>78999</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521353</v>
+        <v>521260</v>
       </c>
       <c r="R128" t="n">
-        <v>7008975</v>
+        <v>7008980</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14258,12 +14258,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14290,7 +14290,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132934718</v>
+        <v>132934719</v>
       </c>
       <c r="B129" t="n">
         <v>78999</v>
@@ -14325,10 +14325,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>521260</v>
+        <v>521236</v>
       </c>
       <c r="R129" t="n">
-        <v>7008980</v>
+        <v>7009013</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,32 +14387,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132934719</v>
+        <v>132934687</v>
       </c>
       <c r="B130" t="n">
-        <v>78999</v>
+        <v>92092</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14422,10 +14422,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>521236</v>
+        <v>521353</v>
       </c>
       <c r="R130" t="n">
-        <v>7009013</v>
+        <v>7008975</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14452,12 +14452,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14775,10 +14775,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132934568</v>
+        <v>132934714</v>
       </c>
       <c r="B134" t="n">
-        <v>79952</v>
+        <v>78999</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>521278</v>
+        <v>521381</v>
       </c>
       <c r="R134" t="n">
-        <v>7008986</v>
+        <v>7008904</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14872,32 +14872,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132934694</v>
+        <v>132934686</v>
       </c>
       <c r="B135" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>521463</v>
+        <v>521364</v>
       </c>
       <c r="R135" t="n">
-        <v>7008881</v>
+        <v>7008948</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14937,12 +14937,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14969,10 +14969,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132934714</v>
+        <v>132934568</v>
       </c>
       <c r="B136" t="n">
-        <v>78999</v>
+        <v>79952</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14980,21 +14980,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15004,10 +15004,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>521381</v>
+        <v>521278</v>
       </c>
       <c r="R136" t="n">
-        <v>7008904</v>
+        <v>7008986</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15066,32 +15066,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132934686</v>
+        <v>132934694</v>
       </c>
       <c r="B137" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>521364</v>
+        <v>521463</v>
       </c>
       <c r="R137" t="n">
-        <v>7008948</v>
+        <v>7008881</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15357,32 +15357,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132934648</v>
+        <v>132934652</v>
       </c>
       <c r="B140" t="n">
-        <v>80305</v>
+        <v>80398</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>385</v>
+        <v>229497</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>521468</v>
+        <v>521312</v>
       </c>
       <c r="R140" t="n">
-        <v>7008870</v>
+        <v>7009003</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15430,13 +15430,17 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15455,10 +15459,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132934509</v>
+        <v>132934578</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>79923</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15466,34 +15470,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>521329</v>
+        <v>521336</v>
       </c>
       <c r="R141" t="n">
-        <v>7009049</v>
+        <v>7008869</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15520,12 +15524,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15552,32 +15556,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934636</v>
+        <v>132934653</v>
       </c>
       <c r="B142" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15587,10 +15591,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521362</v>
+        <v>521357</v>
       </c>
       <c r="R142" t="n">
-        <v>7009037</v>
+        <v>7009035</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15649,32 +15653,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934537</v>
+        <v>132934536</v>
       </c>
       <c r="B143" t="n">
-        <v>79090</v>
+        <v>80398</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15684,10 +15688,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521253</v>
+        <v>521324</v>
       </c>
       <c r="R143" t="n">
-        <v>7009010</v>
+        <v>7009052</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15746,32 +15750,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934561</v>
+        <v>132934648</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>80305</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3242</v>
+        <v>385</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15781,10 +15785,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521263</v>
+        <v>521468</v>
       </c>
       <c r="R144" t="n">
-        <v>7008978</v>
+        <v>7008870</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15825,6 +15829,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15843,45 +15848,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132934652</v>
+        <v>132934509</v>
       </c>
       <c r="B145" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>521312</v>
+        <v>521329</v>
       </c>
       <c r="R145" t="n">
-        <v>7009003</v>
+        <v>7009049</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15908,17 +15913,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15945,10 +15945,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132934578</v>
+        <v>132934636</v>
       </c>
       <c r="B146" t="n">
-        <v>79923</v>
+        <v>80438</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>521336</v>
+        <v>521362</v>
       </c>
       <c r="R146" t="n">
-        <v>7008869</v>
+        <v>7009037</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16010,12 +16010,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16042,45 +16042,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132934653</v>
+        <v>132934537</v>
       </c>
       <c r="B147" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>521357</v>
+        <v>521253</v>
       </c>
       <c r="R147" t="n">
-        <v>7009035</v>
+        <v>7009010</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16139,45 +16139,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132934536</v>
+        <v>132934561</v>
       </c>
       <c r="B148" t="n">
-        <v>80398</v>
+        <v>91840</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229497</v>
+        <v>3242</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>521324</v>
+        <v>521263</v>
       </c>
       <c r="R148" t="n">
-        <v>7009052</v>
+        <v>7008978</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16204,12 +16204,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R2" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,26 +764,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B3" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R3" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +857,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,6 +875,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1626,42 +1626,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132811916</v>
+        <v>132811932</v>
       </c>
       <c r="B10" t="n">
-        <v>104642</v>
+        <v>80438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521428</v>
+        <v>521288</v>
       </c>
       <c r="R10" t="n">
-        <v>7008979</v>
+        <v>7008966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,11 +1706,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,7 +1718,32 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En högstubbe.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula # En högstubbe.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1742,41 +1761,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132811932</v>
+        <v>132811916</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>104642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521288</v>
+        <v>521428</v>
       </c>
       <c r="R11" t="n">
-        <v>7008966</v>
+        <v>7008979</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,6 +1842,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1834,32 +1859,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En högstubbe.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula # En högstubbe.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2912,48 +2912,65 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811968</v>
+        <v>132811944</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521278</v>
+        <v>521377</v>
       </c>
       <c r="R20" t="n">
-        <v>7009051</v>
+        <v>7009007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2988,6 +3005,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3001,26 +3023,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3038,7 +3040,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811970</v>
+        <v>132811968</v>
       </c>
       <c r="B21" t="n">
         <v>79333</v>
@@ -3076,10 +3078,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521326</v>
+        <v>521278</v>
       </c>
       <c r="R21" t="n">
-        <v>7008987</v>
+        <v>7009051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,65 +3166,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811944</v>
+        <v>132811970</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521377</v>
+        <v>521326</v>
       </c>
       <c r="R22" t="n">
-        <v>7009007</v>
+        <v>7008987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,11 +3242,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3275,6 +3255,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132811973</v>
+        <v>132811903</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,21 +3303,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521264</v>
+        <v>521252</v>
       </c>
       <c r="R23" t="n">
         <v>7009005</v>
@@ -3368,6 +3368,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På silverved av tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3380,7 +3385,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3395,12 +3400,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3418,10 +3423,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132811903</v>
+        <v>132811973</v>
       </c>
       <c r="B24" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,21 +3434,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3456,7 +3461,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521252</v>
+        <v>521264</v>
       </c>
       <c r="R24" t="n">
         <v>7009005</v>
@@ -3494,11 +3499,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På silverved av tallhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811924</v>
+        <v>132811988</v>
       </c>
       <c r="B30" t="n">
-        <v>80466</v>
+        <v>101338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4190,26 +4190,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521413</v>
+        <v>521434</v>
       </c>
       <c r="R30" t="n">
-        <v>7008949</v>
+        <v>7008976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4255,6 +4260,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4267,7 +4277,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4411,10 +4421,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811914</v>
+        <v>132811924</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>80466</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4422,46 +4432,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521257</v>
+        <v>521413</v>
       </c>
       <c r="R32" t="n">
-        <v>7008967</v>
+        <v>7008949</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4496,23 +4497,19 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4530,50 +4527,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811949</v>
+        <v>132811914</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4585,10 +4574,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521297</v>
+        <v>521257</v>
       </c>
       <c r="R33" t="n">
-        <v>7009058</v>
+        <v>7008967</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4625,7 +4614,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4634,13 +4623,12 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4658,53 +4646,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811988</v>
+        <v>132811949</v>
       </c>
       <c r="B34" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521434</v>
+        <v>521297</v>
       </c>
       <c r="R34" t="n">
-        <v>7008976</v>
+        <v>7009058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5416,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132840103</v>
+        <v>132840108</v>
       </c>
       <c r="B41" t="n">
-        <v>83315</v>
+        <v>91918</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521403</v>
+        <v>521417</v>
       </c>
       <c r="R41" t="n">
-        <v>7008996</v>
+        <v>7008986</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840108</v>
+        <v>132840103</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521417</v>
+        <v>521403</v>
       </c>
       <c r="R42" t="n">
-        <v>7008986</v>
+        <v>7008996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132840120</v>
+        <v>132840110</v>
       </c>
       <c r="B44" t="n">
-        <v>80304</v>
+        <v>83315</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521467</v>
+        <v>521479</v>
       </c>
       <c r="R44" t="n">
-        <v>7008865</v>
+        <v>7008951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132840110</v>
+        <v>132840106</v>
       </c>
       <c r="B45" t="n">
-        <v>83315</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521479</v>
+        <v>521412</v>
       </c>
       <c r="R45" t="n">
-        <v>7008951</v>
+        <v>7008994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132840106</v>
+        <v>132840120</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>80304</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521412</v>
+        <v>521467</v>
       </c>
       <c r="R46" t="n">
-        <v>7008994</v>
+        <v>7008865</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840099</v>
+        <v>132840123</v>
       </c>
       <c r="B58" t="n">
-        <v>92217</v>
+        <v>79091</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521388</v>
+        <v>521310</v>
       </c>
       <c r="R58" t="n">
-        <v>7009026</v>
+        <v>7008918</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840123</v>
+        <v>132840099</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>92217</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521310</v>
+        <v>521388</v>
       </c>
       <c r="R60" t="n">
-        <v>7008918</v>
+        <v>7009026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7960,32 +7960,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132934683</v>
+        <v>132934698</v>
       </c>
       <c r="B64" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521412</v>
+        <v>521353</v>
       </c>
       <c r="R64" t="n">
-        <v>7008950</v>
+        <v>7008984</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8057,10 +8057,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132934698</v>
+        <v>132934638</v>
       </c>
       <c r="B65" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8068,21 +8068,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521353</v>
+        <v>521314</v>
       </c>
       <c r="R65" t="n">
-        <v>7008984</v>
+        <v>7009064</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8154,10 +8154,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934638</v>
+        <v>132934540</v>
       </c>
       <c r="B66" t="n">
-        <v>80438</v>
+        <v>79090</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8165,34 +8165,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521314</v>
+        <v>521347</v>
       </c>
       <c r="R66" t="n">
-        <v>7009064</v>
+        <v>7008990</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8251,10 +8251,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934540</v>
+        <v>132934556</v>
       </c>
       <c r="B67" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521347</v>
+        <v>521357</v>
       </c>
       <c r="R67" t="n">
-        <v>7008990</v>
+        <v>7008968</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,6 +8322,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8348,10 +8353,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934556</v>
+        <v>132934639</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,34 +8364,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521357</v>
+        <v>521297</v>
       </c>
       <c r="R68" t="n">
-        <v>7008968</v>
+        <v>7009054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8419,11 +8424,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8450,32 +8450,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934639</v>
+        <v>132934683</v>
       </c>
       <c r="B69" t="n">
-        <v>80438</v>
+        <v>92092</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521297</v>
+        <v>521412</v>
       </c>
       <c r="R69" t="n">
-        <v>7009054</v>
+        <v>7008950</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8547,32 +8547,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132934654</v>
+        <v>132934632</v>
       </c>
       <c r="B70" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521338</v>
+        <v>521385</v>
       </c>
       <c r="R70" t="n">
-        <v>7009053</v>
+        <v>7009021</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8644,32 +8644,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132934632</v>
+        <v>132934654</v>
       </c>
       <c r="B71" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8679,10 +8679,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521385</v>
+        <v>521338</v>
       </c>
       <c r="R71" t="n">
-        <v>7009021</v>
+        <v>7009053</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8741,32 +8741,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934656</v>
+        <v>132934635</v>
       </c>
       <c r="B72" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521300</v>
+        <v>521346</v>
       </c>
       <c r="R72" t="n">
-        <v>7009071</v>
+        <v>7008992</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8838,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934617</v>
+        <v>132934708</v>
       </c>
       <c r="B73" t="n">
-        <v>91971</v>
+        <v>79333</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521420</v>
+        <v>521276</v>
       </c>
       <c r="R73" t="n">
-        <v>7008863</v>
+        <v>7009057</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8903,12 +8903,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8935,42 +8935,42 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934713</v>
+        <v>132934538</v>
       </c>
       <c r="B74" t="n">
-        <v>92192</v>
+        <v>79090</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521238</v>
+        <v>521314</v>
       </c>
       <c r="R74" t="n">
         <v>7008997</v>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9032,32 +9032,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934635</v>
+        <v>132934656</v>
       </c>
       <c r="B75" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521346</v>
+        <v>521300</v>
       </c>
       <c r="R75" t="n">
-        <v>7008992</v>
+        <v>7009071</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934708</v>
+        <v>132934713</v>
       </c>
       <c r="B76" t="n">
-        <v>79333</v>
+        <v>92192</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521276</v>
+        <v>521238</v>
       </c>
       <c r="R76" t="n">
-        <v>7009057</v>
+        <v>7008997</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9226,10 +9226,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934538</v>
+        <v>132934617</v>
       </c>
       <c r="B77" t="n">
-        <v>79090</v>
+        <v>91971</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9237,34 +9237,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521314</v>
+        <v>521420</v>
       </c>
       <c r="R77" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9291,12 +9291,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9614,32 +9614,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934688</v>
+        <v>132934623</v>
       </c>
       <c r="B81" t="n">
-        <v>92092</v>
+        <v>79091</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521335</v>
+        <v>521457</v>
       </c>
       <c r="R81" t="n">
-        <v>7009020</v>
+        <v>7008866</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9711,10 +9711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934563</v>
+        <v>132934624</v>
       </c>
       <c r="B82" t="n">
-        <v>97370</v>
+        <v>79091</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521415</v>
+        <v>521279</v>
       </c>
       <c r="R82" t="n">
-        <v>7008980</v>
+        <v>7008952</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934706</v>
+        <v>132934563</v>
       </c>
       <c r="B83" t="n">
-        <v>79333</v>
+        <v>97370</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521426</v>
+        <v>521415</v>
       </c>
       <c r="R83" t="n">
-        <v>7008976</v>
+        <v>7008980</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934707</v>
+        <v>132934688</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521289</v>
+        <v>521335</v>
       </c>
       <c r="R84" t="n">
-        <v>7008957</v>
+        <v>7009020</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9970,12 +9970,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10002,32 +10002,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934721</v>
+        <v>132934706</v>
       </c>
       <c r="B85" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521464</v>
+        <v>521426</v>
       </c>
       <c r="R85" t="n">
-        <v>7008859</v>
+        <v>7008976</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10099,32 +10099,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934624</v>
+        <v>132934721</v>
       </c>
       <c r="B86" t="n">
-        <v>79091</v>
+        <v>93206</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521279</v>
+        <v>521464</v>
       </c>
       <c r="R86" t="n">
-        <v>7008952</v>
+        <v>7008859</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934623</v>
+        <v>132934707</v>
       </c>
       <c r="B87" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10207,21 +10207,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521457</v>
+        <v>521289</v>
       </c>
       <c r="R87" t="n">
-        <v>7008866</v>
+        <v>7008957</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10390,7 +10390,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132934700</v>
+        <v>132934692</v>
       </c>
       <c r="B89" t="n">
         <v>79333</v>
@@ -10425,10 +10425,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>521305</v>
+        <v>521355</v>
       </c>
       <c r="R89" t="n">
-        <v>7009061</v>
+        <v>7008924</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10487,7 +10487,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934692</v>
+        <v>132934700</v>
       </c>
       <c r="B90" t="n">
         <v>79333</v>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521355</v>
+        <v>521305</v>
       </c>
       <c r="R90" t="n">
-        <v>7008924</v>
+        <v>7009061</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10552,12 +10552,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10584,45 +10584,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934668</v>
+        <v>132934508</v>
       </c>
       <c r="B91" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521460</v>
+        <v>521332</v>
       </c>
       <c r="R91" t="n">
-        <v>7008862</v>
+        <v>7009041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,17 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10686,32 +10681,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934657</v>
+        <v>132934711</v>
       </c>
       <c r="B92" t="n">
-        <v>80398</v>
+        <v>92192</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229497</v>
+        <v>65</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10721,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521311</v>
+        <v>521269</v>
       </c>
       <c r="R92" t="n">
-        <v>7009049</v>
+        <v>7008900</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10751,12 +10746,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10783,10 +10778,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934508</v>
+        <v>132934661</v>
       </c>
       <c r="B93" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10794,34 +10789,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521332</v>
+        <v>521456</v>
       </c>
       <c r="R93" t="n">
-        <v>7009041</v>
+        <v>7008920</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10848,12 +10843,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10880,32 +10875,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934711</v>
+        <v>132934705</v>
       </c>
       <c r="B94" t="n">
-        <v>92192</v>
+        <v>79333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10915,10 +10910,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521269</v>
+        <v>521416</v>
       </c>
       <c r="R94" t="n">
-        <v>7008900</v>
+        <v>7008940</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10977,10 +10972,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934661</v>
+        <v>132934699</v>
       </c>
       <c r="B95" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10988,21 +10983,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521456</v>
+        <v>521371</v>
       </c>
       <c r="R95" t="n">
-        <v>7008920</v>
+        <v>7009040</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11042,12 +11037,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11074,32 +11069,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934705</v>
+        <v>132934723</v>
       </c>
       <c r="B96" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11109,10 +11104,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521416</v>
+        <v>521262</v>
       </c>
       <c r="R96" t="n">
-        <v>7008940</v>
+        <v>7009041</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11171,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934699</v>
+        <v>132934668</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11206,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521371</v>
+        <v>521460</v>
       </c>
       <c r="R97" t="n">
-        <v>7009040</v>
+        <v>7008862</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11236,12 +11231,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11268,10 +11268,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934723</v>
+        <v>132934657</v>
       </c>
       <c r="B98" t="n">
-        <v>93206</v>
+        <v>80398</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11279,21 +11279,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521262</v>
+        <v>521311</v>
       </c>
       <c r="R98" t="n">
-        <v>7009041</v>
+        <v>7009049</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11462,45 +11462,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934505</v>
+        <v>132934603</v>
       </c>
       <c r="B100" t="n">
-        <v>97370</v>
+        <v>80342</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521304</v>
+        <v>521339</v>
       </c>
       <c r="R100" t="n">
-        <v>7009055</v>
+        <v>7009060</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11559,32 +11559,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934603</v>
+        <v>132934580</v>
       </c>
       <c r="B101" t="n">
-        <v>80342</v>
+        <v>79923</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6456</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11594,10 +11594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521339</v>
+        <v>521256</v>
       </c>
       <c r="R101" t="n">
-        <v>7009060</v>
+        <v>7008979</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11850,10 +11850,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934580</v>
+        <v>132934505</v>
       </c>
       <c r="B104" t="n">
-        <v>79923</v>
+        <v>97370</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11861,34 +11861,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521256</v>
+        <v>521304</v>
       </c>
       <c r="R104" t="n">
-        <v>7008979</v>
+        <v>7009055</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11915,12 +11915,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13708,32 +13708,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934720</v>
+        <v>132934622</v>
       </c>
       <c r="B123" t="n">
-        <v>93206</v>
+        <v>79091</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521341</v>
+        <v>521453</v>
       </c>
       <c r="R123" t="n">
-        <v>7008936</v>
+        <v>7008881</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934731</v>
+        <v>132934720</v>
       </c>
       <c r="B124" t="n">
-        <v>78340</v>
+        <v>93206</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521235</v>
+        <v>521341</v>
       </c>
       <c r="R124" t="n">
-        <v>7009006</v>
+        <v>7008936</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934622</v>
+        <v>132934731</v>
       </c>
       <c r="B125" t="n">
-        <v>79091</v>
+        <v>78340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521453</v>
+        <v>521235</v>
       </c>
       <c r="R125" t="n">
-        <v>7008881</v>
+        <v>7009006</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15357,32 +15357,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132934652</v>
+        <v>132934648</v>
       </c>
       <c r="B140" t="n">
-        <v>80398</v>
+        <v>80305</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229497</v>
+        <v>385</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>521312</v>
+        <v>521468</v>
       </c>
       <c r="R140" t="n">
-        <v>7009003</v>
+        <v>7008870</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15430,17 +15430,13 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15459,10 +15455,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132934578</v>
+        <v>132934509</v>
       </c>
       <c r="B141" t="n">
-        <v>79923</v>
+        <v>91918</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15470,34 +15466,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>521336</v>
+        <v>521329</v>
       </c>
       <c r="R141" t="n">
-        <v>7008869</v>
+        <v>7009049</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15524,12 +15520,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15556,32 +15552,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934653</v>
+        <v>132934636</v>
       </c>
       <c r="B142" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15591,10 +15587,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521357</v>
+        <v>521362</v>
       </c>
       <c r="R142" t="n">
-        <v>7009035</v>
+        <v>7009037</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15653,32 +15649,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934536</v>
+        <v>132934537</v>
       </c>
       <c r="B143" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15688,10 +15684,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521324</v>
+        <v>521253</v>
       </c>
       <c r="R143" t="n">
-        <v>7009052</v>
+        <v>7009010</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15750,32 +15746,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934648</v>
+        <v>132934561</v>
       </c>
       <c r="B144" t="n">
-        <v>80305</v>
+        <v>91840</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>385</v>
+        <v>3242</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15785,10 +15781,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521468</v>
+        <v>521263</v>
       </c>
       <c r="R144" t="n">
-        <v>7008870</v>
+        <v>7008978</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15829,7 +15825,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15848,10 +15843,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132934509</v>
+        <v>132934578</v>
       </c>
       <c r="B145" t="n">
-        <v>91918</v>
+        <v>79923</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15859,34 +15854,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>521329</v>
+        <v>521336</v>
       </c>
       <c r="R145" t="n">
-        <v>7009049</v>
+        <v>7008869</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15913,12 +15908,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15945,32 +15940,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132934636</v>
+        <v>132934653</v>
       </c>
       <c r="B146" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15975,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>521362</v>
+        <v>521357</v>
       </c>
       <c r="R146" t="n">
-        <v>7009037</v>
+        <v>7009035</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16042,32 +16037,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132934537</v>
+        <v>132934536</v>
       </c>
       <c r="B147" t="n">
-        <v>79090</v>
+        <v>80398</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16077,10 +16072,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>521253</v>
+        <v>521324</v>
       </c>
       <c r="R147" t="n">
-        <v>7009010</v>
+        <v>7009052</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16139,32 +16134,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132934561</v>
+        <v>132934652</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>80398</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3242</v>
+        <v>229497</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16174,10 +16169,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>521263</v>
+        <v>521312</v>
       </c>
       <c r="R148" t="n">
-        <v>7008978</v>
+        <v>7009003</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16210,6 +16205,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R2" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,32 +806,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R3" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +882,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,26 +895,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1023,65 +1023,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132811946</v>
+        <v>132811986</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521337</v>
+        <v>521479</v>
       </c>
       <c r="R5" t="n">
-        <v>7009020</v>
+        <v>7008956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,11 +1104,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 1 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,7 +1116,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,53 +1134,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132811986</v>
+        <v>132811946</v>
       </c>
       <c r="B6" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521479</v>
+        <v>521337</v>
       </c>
       <c r="R6" t="n">
-        <v>7008956</v>
+        <v>7009020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,6 +1227,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 1 m2 yta i tallskog.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132811929</v>
+        <v>132811968</v>
       </c>
       <c r="B18" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521300</v>
+        <v>521278</v>
       </c>
       <c r="R18" t="n">
-        <v>7009023</v>
+        <v>7009051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,11 +2731,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad tallved i tallskog.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2763,12 +2758,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2786,10 +2781,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811902</v>
+        <v>132811970</v>
       </c>
       <c r="B19" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2797,21 +2792,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521234</v>
+        <v>521326</v>
       </c>
       <c r="R19" t="n">
-        <v>7008999</v>
+        <v>7008987</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2874,7 +2869,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2889,12 +2884,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2912,65 +2907,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811944</v>
+        <v>132811929</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>79091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521377</v>
+        <v>521300</v>
       </c>
       <c r="R20" t="n">
-        <v>7009007</v>
+        <v>7009023</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,7 +2985,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
+          <t>På kolad tallved i tallskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3023,6 +3001,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3040,10 +3038,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811968</v>
+        <v>132811902</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,21 +3049,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3078,10 +3076,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521278</v>
+        <v>521234</v>
       </c>
       <c r="R21" t="n">
-        <v>7009051</v>
+        <v>7008999</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3128,7 +3126,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3143,12 +3141,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,48 +3164,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811970</v>
+        <v>132811944</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521326</v>
+        <v>521377</v>
       </c>
       <c r="R22" t="n">
-        <v>7008987</v>
+        <v>7009007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3242,6 +3257,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3255,26 +3275,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3814,65 +3814,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132811948</v>
+        <v>132811965</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521326</v>
+        <v>521397</v>
       </c>
       <c r="R27" t="n">
-        <v>7009043</v>
+        <v>7008961</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3907,11 +3890,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor inom ca 3 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3924,7 +3902,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3942,48 +3940,65 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132811965</v>
+        <v>132811948</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521397</v>
+        <v>521326</v>
       </c>
       <c r="R28" t="n">
-        <v>7008961</v>
+        <v>7009043</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4018,6 +4033,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor inom ca 3 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4030,27 +4050,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4179,10 +4179,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811988</v>
+        <v>132811924</v>
       </c>
       <c r="B30" t="n">
-        <v>101338</v>
+        <v>80466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4190,31 +4190,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521434</v>
+        <v>521413</v>
       </c>
       <c r="R30" t="n">
-        <v>7008976</v>
+        <v>7008949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4260,11 +4255,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4277,7 +4267,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4421,10 +4411,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811924</v>
+        <v>132811914</v>
       </c>
       <c r="B32" t="n">
-        <v>80466</v>
+        <v>57145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4432,37 +4422,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521413</v>
+        <v>521257</v>
       </c>
       <c r="R32" t="n">
-        <v>7008949</v>
+        <v>7008967</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4497,19 +4496,23 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4527,10 +4530,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811914</v>
+        <v>132811988</v>
       </c>
       <c r="B33" t="n">
-        <v>57145</v>
+        <v>101338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4538,46 +4541,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521257</v>
+        <v>521434</v>
       </c>
       <c r="R33" t="n">
-        <v>7008967</v>
+        <v>7008976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4614,7 +4613,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4623,12 +4622,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132840108</v>
+        <v>132840103</v>
       </c>
       <c r="B41" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521417</v>
+        <v>521403</v>
       </c>
       <c r="R41" t="n">
-        <v>7008986</v>
+        <v>7008996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840103</v>
+        <v>132840111</v>
       </c>
       <c r="B42" t="n">
-        <v>83315</v>
+        <v>78345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521403</v>
+        <v>521478</v>
       </c>
       <c r="R42" t="n">
-        <v>7008996</v>
+        <v>7008952</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132840111</v>
+        <v>132840108</v>
       </c>
       <c r="B43" t="n">
-        <v>78345</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521478</v>
+        <v>521417</v>
       </c>
       <c r="R43" t="n">
-        <v>7008952</v>
+        <v>7008986</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132840110</v>
+        <v>132840120</v>
       </c>
       <c r="B44" t="n">
-        <v>83315</v>
+        <v>80304</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>388</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521479</v>
+        <v>521467</v>
       </c>
       <c r="R44" t="n">
-        <v>7008951</v>
+        <v>7008865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132840106</v>
+        <v>132840110</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>83315</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521412</v>
+        <v>521479</v>
       </c>
       <c r="R45" t="n">
-        <v>7008994</v>
+        <v>7008951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132840120</v>
+        <v>132840106</v>
       </c>
       <c r="B46" t="n">
-        <v>80304</v>
+        <v>79333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521467</v>
+        <v>521412</v>
       </c>
       <c r="R46" t="n">
-        <v>7008865</v>
+        <v>7008994</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6165,32 +6165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132840113</v>
+        <v>132840124</v>
       </c>
       <c r="B48" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521480</v>
+        <v>521308</v>
       </c>
       <c r="R48" t="n">
-        <v>7008948</v>
+        <v>7008922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6272,7 +6272,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132840124</v>
+        <v>132840091</v>
       </c>
       <c r="B49" t="n">
         <v>79333</v>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521308</v>
+        <v>521310</v>
       </c>
       <c r="R49" t="n">
-        <v>7008922</v>
+        <v>7009002</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6363,6 +6363,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6379,32 +6394,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132840091</v>
+        <v>132840113</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6414,10 +6429,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521310</v>
+        <v>521480</v>
       </c>
       <c r="R50" t="n">
-        <v>7009002</v>
+        <v>7008948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6449,7 +6464,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6459,7 +6474,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6470,21 +6485,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840123</v>
+        <v>132840099</v>
       </c>
       <c r="B58" t="n">
-        <v>79091</v>
+        <v>92217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521310</v>
+        <v>521388</v>
       </c>
       <c r="R58" t="n">
-        <v>7008918</v>
+        <v>7009026</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840099</v>
+        <v>132840123</v>
       </c>
       <c r="B60" t="n">
-        <v>92217</v>
+        <v>79091</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521388</v>
+        <v>521310</v>
       </c>
       <c r="R60" t="n">
-        <v>7009026</v>
+        <v>7008918</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8154,45 +8154,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934540</v>
+        <v>132934683</v>
       </c>
       <c r="B66" t="n">
-        <v>79090</v>
+        <v>92092</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521347</v>
+        <v>521412</v>
       </c>
       <c r="R66" t="n">
-        <v>7008990</v>
+        <v>7008950</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934556</v>
+        <v>132934540</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521357</v>
+        <v>521347</v>
       </c>
       <c r="R67" t="n">
-        <v>7008968</v>
+        <v>7008990</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,11 +8322,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8353,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934639</v>
+        <v>132934556</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8364,34 +8359,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521297</v>
+        <v>521357</v>
       </c>
       <c r="R68" t="n">
-        <v>7009054</v>
+        <v>7008968</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8424,6 +8419,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8450,32 +8450,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934683</v>
+        <v>132934639</v>
       </c>
       <c r="B69" t="n">
-        <v>92092</v>
+        <v>80438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521412</v>
+        <v>521297</v>
       </c>
       <c r="R69" t="n">
-        <v>7008950</v>
+        <v>7009054</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8741,32 +8741,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934635</v>
+        <v>132934713</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>92192</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521346</v>
+        <v>521238</v>
       </c>
       <c r="R72" t="n">
-        <v>7008992</v>
+        <v>7008997</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8838,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934708</v>
+        <v>132934635</v>
       </c>
       <c r="B73" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521276</v>
+        <v>521346</v>
       </c>
       <c r="R73" t="n">
-        <v>7009057</v>
+        <v>7008992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934538</v>
+        <v>132934708</v>
       </c>
       <c r="B74" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8946,34 +8946,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521314</v>
+        <v>521276</v>
       </c>
       <c r="R74" t="n">
-        <v>7008997</v>
+        <v>7009057</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9032,45 +9032,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934656</v>
+        <v>132934538</v>
       </c>
       <c r="B75" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521300</v>
+        <v>521314</v>
       </c>
       <c r="R75" t="n">
-        <v>7009071</v>
+        <v>7008997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934713</v>
+        <v>132934617</v>
       </c>
       <c r="B76" t="n">
-        <v>92192</v>
+        <v>91971</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521238</v>
+        <v>521420</v>
       </c>
       <c r="R76" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9226,32 +9226,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934617</v>
+        <v>132934656</v>
       </c>
       <c r="B77" t="n">
-        <v>91971</v>
+        <v>80398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9261,10 +9261,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521420</v>
+        <v>521300</v>
       </c>
       <c r="R77" t="n">
-        <v>7008863</v>
+        <v>7009071</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9291,12 +9291,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9614,10 +9614,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934623</v>
+        <v>132934563</v>
       </c>
       <c r="B81" t="n">
-        <v>79091</v>
+        <v>97370</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9625,21 +9625,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521457</v>
+        <v>521415</v>
       </c>
       <c r="R81" t="n">
-        <v>7008866</v>
+        <v>7008980</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9711,10 +9711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934624</v>
+        <v>132934706</v>
       </c>
       <c r="B82" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521279</v>
+        <v>521426</v>
       </c>
       <c r="R82" t="n">
-        <v>7008952</v>
+        <v>7008976</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934563</v>
+        <v>132934688</v>
       </c>
       <c r="B83" t="n">
-        <v>97370</v>
+        <v>92092</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521415</v>
+        <v>521335</v>
       </c>
       <c r="R83" t="n">
-        <v>7008980</v>
+        <v>7009020</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934688</v>
+        <v>132934707</v>
       </c>
       <c r="B84" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521335</v>
+        <v>521289</v>
       </c>
       <c r="R84" t="n">
-        <v>7009020</v>
+        <v>7008957</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9970,12 +9970,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10002,32 +10002,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934706</v>
+        <v>132934721</v>
       </c>
       <c r="B85" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521426</v>
+        <v>521464</v>
       </c>
       <c r="R85" t="n">
-        <v>7008976</v>
+        <v>7008859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10099,32 +10099,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934721</v>
+        <v>132934624</v>
       </c>
       <c r="B86" t="n">
-        <v>93206</v>
+        <v>79091</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521464</v>
+        <v>521279</v>
       </c>
       <c r="R86" t="n">
-        <v>7008859</v>
+        <v>7008952</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934707</v>
+        <v>132934623</v>
       </c>
       <c r="B87" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10207,21 +10207,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521289</v>
+        <v>521457</v>
       </c>
       <c r="R87" t="n">
-        <v>7008957</v>
+        <v>7008866</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10293,32 +10293,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132934682</v>
+        <v>132934700</v>
       </c>
       <c r="B88" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10328,10 +10328,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>521469</v>
+        <v>521305</v>
       </c>
       <c r="R88" t="n">
-        <v>7008869</v>
+        <v>7009061</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10358,12 +10358,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10487,32 +10487,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132934700</v>
+        <v>132934682</v>
       </c>
       <c r="B90" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>521305</v>
+        <v>521469</v>
       </c>
       <c r="R90" t="n">
-        <v>7009061</v>
+        <v>7008869</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10552,12 +10552,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10584,45 +10584,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934508</v>
+        <v>132934711</v>
       </c>
       <c r="B91" t="n">
-        <v>91918</v>
+        <v>92192</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521332</v>
+        <v>521269</v>
       </c>
       <c r="R91" t="n">
-        <v>7009041</v>
+        <v>7008900</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,45 +10681,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934711</v>
+        <v>132934508</v>
       </c>
       <c r="B92" t="n">
-        <v>92192</v>
+        <v>91918</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521269</v>
+        <v>521332</v>
       </c>
       <c r="R92" t="n">
-        <v>7008900</v>
+        <v>7009041</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10746,12 +10746,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11365,45 +11365,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934685</v>
+        <v>132934505</v>
       </c>
       <c r="B99" t="n">
-        <v>92092</v>
+        <v>97370</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521278</v>
+        <v>521304</v>
       </c>
       <c r="R99" t="n">
-        <v>7008985</v>
+        <v>7009055</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11462,32 +11462,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934603</v>
+        <v>132934685</v>
       </c>
       <c r="B100" t="n">
-        <v>80342</v>
+        <v>92092</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521339</v>
+        <v>521278</v>
       </c>
       <c r="R100" t="n">
-        <v>7009060</v>
+        <v>7008985</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11559,32 +11559,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934580</v>
+        <v>132934603</v>
       </c>
       <c r="B101" t="n">
-        <v>79923</v>
+        <v>80342</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11594,10 +11594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521256</v>
+        <v>521339</v>
       </c>
       <c r="R101" t="n">
-        <v>7008979</v>
+        <v>7009060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11656,7 +11656,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934520</v>
+        <v>132934621</v>
       </c>
       <c r="B102" t="n">
         <v>79091</v>
@@ -11687,14 +11687,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521367</v>
+        <v>521284</v>
       </c>
       <c r="R102" t="n">
-        <v>7008928</v>
+        <v>7008883</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11721,12 +11721,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11753,10 +11753,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934621</v>
+        <v>132934580</v>
       </c>
       <c r="B103" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11764,21 +11764,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521284</v>
+        <v>521256</v>
       </c>
       <c r="R103" t="n">
-        <v>7008883</v>
+        <v>7008979</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11850,10 +11850,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934505</v>
+        <v>132934520</v>
       </c>
       <c r="B104" t="n">
-        <v>97370</v>
+        <v>79091</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11861,21 +11861,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11885,10 +11885,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521304</v>
+        <v>521367</v>
       </c>
       <c r="R104" t="n">
-        <v>7009055</v>
+        <v>7008928</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11947,32 +11947,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934643</v>
+        <v>132934649</v>
       </c>
       <c r="B105" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521368</v>
+        <v>521472</v>
       </c>
       <c r="R105" t="n">
-        <v>7009037</v>
+        <v>7008923</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934669</v>
+        <v>132934643</v>
       </c>
       <c r="B106" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521481</v>
+        <v>521368</v>
       </c>
       <c r="R106" t="n">
-        <v>7008912</v>
+        <v>7009037</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,11 +12115,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12146,32 +12141,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B107" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12181,10 +12176,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R107" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12217,6 +12212,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12243,10 +12243,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132934715</v>
+        <v>132934637</v>
       </c>
       <c r="B108" t="n">
-        <v>78999</v>
+        <v>80438</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12254,21 +12254,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>521370</v>
+        <v>521330</v>
       </c>
       <c r="R108" t="n">
-        <v>7008865</v>
+        <v>7009056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12308,12 +12308,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12437,10 +12442,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934637</v>
+        <v>132934715</v>
       </c>
       <c r="B110" t="n">
-        <v>80438</v>
+        <v>78999</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12448,21 +12453,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12472,10 +12477,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521330</v>
+        <v>521370</v>
       </c>
       <c r="R110" t="n">
-        <v>7009056</v>
+        <v>7008865</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12502,17 +12507,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12539,32 +12539,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934651</v>
+        <v>132934645</v>
       </c>
       <c r="B111" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521370</v>
+        <v>521343</v>
       </c>
       <c r="R111" t="n">
-        <v>7009038</v>
+        <v>7009058</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12604,12 +12604,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12636,32 +12641,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934645</v>
+        <v>132934651</v>
       </c>
       <c r="B112" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12671,10 +12676,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521343</v>
+        <v>521370</v>
       </c>
       <c r="R112" t="n">
-        <v>7009058</v>
+        <v>7009038</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12701,17 +12706,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13708,32 +13708,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934622</v>
+        <v>132934720</v>
       </c>
       <c r="B123" t="n">
-        <v>79091</v>
+        <v>93206</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521453</v>
+        <v>521341</v>
       </c>
       <c r="R123" t="n">
-        <v>7008881</v>
+        <v>7008936</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934720</v>
+        <v>132934731</v>
       </c>
       <c r="B124" t="n">
-        <v>93206</v>
+        <v>78340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521341</v>
+        <v>521235</v>
       </c>
       <c r="R124" t="n">
-        <v>7008936</v>
+        <v>7009006</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934731</v>
+        <v>132934622</v>
       </c>
       <c r="B125" t="n">
-        <v>78340</v>
+        <v>79091</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521235</v>
+        <v>521453</v>
       </c>
       <c r="R125" t="n">
-        <v>7009006</v>
+        <v>7008881</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14193,7 +14193,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934718</v>
+        <v>132934719</v>
       </c>
       <c r="B128" t="n">
         <v>78999</v>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521260</v>
+        <v>521236</v>
       </c>
       <c r="R128" t="n">
-        <v>7008980</v>
+        <v>7009013</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14290,7 +14290,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132934719</v>
+        <v>132934718</v>
       </c>
       <c r="B129" t="n">
         <v>78999</v>
@@ -14325,10 +14325,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>521236</v>
+        <v>521260</v>
       </c>
       <c r="R129" t="n">
-        <v>7009013</v>
+        <v>7008980</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132934714</v>
+        <v>132934568</v>
       </c>
       <c r="B134" t="n">
-        <v>78999</v>
+        <v>79952</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>521381</v>
+        <v>521278</v>
       </c>
       <c r="R134" t="n">
-        <v>7008904</v>
+        <v>7008986</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14872,32 +14872,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132934686</v>
+        <v>132934694</v>
       </c>
       <c r="B135" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14907,10 +14907,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>521364</v>
+        <v>521463</v>
       </c>
       <c r="R135" t="n">
-        <v>7008948</v>
+        <v>7008881</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14937,12 +14937,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14969,32 +14969,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132934568</v>
+        <v>132934686</v>
       </c>
       <c r="B136" t="n">
-        <v>79952</v>
+        <v>92092</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15004,10 +15004,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>521278</v>
+        <v>521364</v>
       </c>
       <c r="R136" t="n">
-        <v>7008986</v>
+        <v>7008948</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15066,10 +15066,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132934694</v>
+        <v>132934519</v>
       </c>
       <c r="B137" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15077,34 +15077,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>521463</v>
+        <v>521418</v>
       </c>
       <c r="R137" t="n">
-        <v>7008881</v>
+        <v>7008891</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15163,10 +15163,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132934519</v>
+        <v>132934579</v>
       </c>
       <c r="B138" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15174,34 +15174,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>521418</v>
+        <v>521343</v>
       </c>
       <c r="R138" t="n">
-        <v>7008891</v>
+        <v>7008898</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15228,12 +15228,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15260,10 +15260,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132934579</v>
+        <v>132934714</v>
       </c>
       <c r="B139" t="n">
-        <v>79923</v>
+        <v>78999</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15271,21 +15271,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>521343</v>
+        <v>521381</v>
       </c>
       <c r="R139" t="n">
-        <v>7008898</v>
+        <v>7008904</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15357,32 +15357,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132934648</v>
+        <v>132934652</v>
       </c>
       <c r="B140" t="n">
-        <v>80305</v>
+        <v>80398</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>385</v>
+        <v>229497</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>521468</v>
+        <v>521312</v>
       </c>
       <c r="R140" t="n">
-        <v>7008870</v>
+        <v>7009003</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15430,13 +15430,17 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15455,10 +15459,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132934509</v>
+        <v>132934578</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>79923</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15466,34 +15470,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>521329</v>
+        <v>521336</v>
       </c>
       <c r="R141" t="n">
-        <v>7009049</v>
+        <v>7008869</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15520,12 +15524,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15552,32 +15556,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934636</v>
+        <v>132934653</v>
       </c>
       <c r="B142" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15587,10 +15591,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521362</v>
+        <v>521357</v>
       </c>
       <c r="R142" t="n">
-        <v>7009037</v>
+        <v>7009035</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15649,32 +15653,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934537</v>
+        <v>132934536</v>
       </c>
       <c r="B143" t="n">
-        <v>79090</v>
+        <v>80398</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15684,10 +15688,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521253</v>
+        <v>521324</v>
       </c>
       <c r="R143" t="n">
-        <v>7009010</v>
+        <v>7009052</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15746,10 +15750,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934561</v>
+        <v>132934509</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>91918</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15757,34 +15761,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3242</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521263</v>
+        <v>521329</v>
       </c>
       <c r="R144" t="n">
-        <v>7008978</v>
+        <v>7009049</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15811,12 +15815,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15843,32 +15847,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132934578</v>
+        <v>132934648</v>
       </c>
       <c r="B145" t="n">
-        <v>79923</v>
+        <v>80305</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>385</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15878,10 +15882,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>521336</v>
+        <v>521468</v>
       </c>
       <c r="R145" t="n">
-        <v>7008869</v>
+        <v>7008870</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15922,6 +15926,7 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15940,32 +15945,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132934653</v>
+        <v>132934636</v>
       </c>
       <c r="B146" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15975,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>521357</v>
+        <v>521362</v>
       </c>
       <c r="R146" t="n">
-        <v>7009035</v>
+        <v>7009037</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16037,32 +16042,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132934536</v>
+        <v>132934537</v>
       </c>
       <c r="B147" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16072,10 +16077,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>521324</v>
+        <v>521253</v>
       </c>
       <c r="R147" t="n">
-        <v>7009052</v>
+        <v>7009010</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16134,32 +16139,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132934652</v>
+        <v>132934561</v>
       </c>
       <c r="B148" t="n">
-        <v>80398</v>
+        <v>91840</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>229497</v>
+        <v>3242</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16169,10 +16174,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>521312</v>
+        <v>521263</v>
       </c>
       <c r="R148" t="n">
-        <v>7009003</v>
+        <v>7008978</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16205,11 +16210,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -1023,53 +1023,65 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132811986</v>
+        <v>132811946</v>
       </c>
       <c r="B5" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521479</v>
+        <v>521337</v>
       </c>
       <c r="R5" t="n">
-        <v>7008956</v>
+        <v>7009020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1116,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 1 m2 yta i tallskog.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1116,7 +1133,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1134,65 +1151,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132811946</v>
+        <v>132811986</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521337</v>
+        <v>521479</v>
       </c>
       <c r="R6" t="n">
-        <v>7009020</v>
+        <v>7008956</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,11 +1232,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 1 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1626,41 +1626,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132811932</v>
+        <v>132811916</v>
       </c>
       <c r="B10" t="n">
-        <v>80438</v>
+        <v>104642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521288</v>
+        <v>521428</v>
       </c>
       <c r="R10" t="n">
-        <v>7008966</v>
+        <v>7008979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,6 +1707,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1718,32 +1724,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En högstubbe.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula # En högstubbe.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1761,42 +1742,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132811916</v>
+        <v>132811932</v>
       </c>
       <c r="B11" t="n">
-        <v>104642</v>
+        <v>80438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1804,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521428</v>
+        <v>521288</v>
       </c>
       <c r="R11" t="n">
-        <v>7008979</v>
+        <v>7008966</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,11 +1822,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1859,7 +1834,32 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>En högstubbe.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula # En högstubbe.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132811968</v>
+        <v>132811929</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521278</v>
+        <v>521300</v>
       </c>
       <c r="R18" t="n">
-        <v>7009051</v>
+        <v>7009023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2731,6 +2731,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad tallved i tallskog.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2758,12 +2763,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2781,10 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811970</v>
+        <v>132811902</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,21 +2797,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521326</v>
+        <v>521234</v>
       </c>
       <c r="R19" t="n">
-        <v>7008987</v>
+        <v>7008999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2869,7 +2874,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2884,12 +2889,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2907,10 +2912,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811929</v>
+        <v>132811968</v>
       </c>
       <c r="B20" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2918,21 +2923,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521300</v>
+        <v>521278</v>
       </c>
       <c r="R20" t="n">
-        <v>7009023</v>
+        <v>7009051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2983,11 +2988,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På kolad tallved i tallskog.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811902</v>
+        <v>132811970</v>
       </c>
       <c r="B21" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521234</v>
+        <v>521326</v>
       </c>
       <c r="R21" t="n">
-        <v>7008999</v>
+        <v>7008987</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132811903</v>
+        <v>132811973</v>
       </c>
       <c r="B23" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,21 +3303,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521252</v>
+        <v>521264</v>
       </c>
       <c r="R23" t="n">
         <v>7009005</v>
@@ -3368,11 +3368,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På silverved av tallhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3385,7 +3380,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3400,12 +3395,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3423,10 +3418,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132811973</v>
+        <v>132811903</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3434,21 +3429,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3461,7 +3456,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521264</v>
+        <v>521252</v>
       </c>
       <c r="R24" t="n">
         <v>7009005</v>
@@ -3499,6 +3494,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På silverved av tallhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811924</v>
+        <v>132811957</v>
       </c>
       <c r="B30" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521413</v>
+        <v>521417</v>
       </c>
       <c r="R30" t="n">
-        <v>7008949</v>
+        <v>7008923</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4268,6 +4268,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,48 +4305,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132811957</v>
+        <v>132811914</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521417</v>
+        <v>521257</v>
       </c>
       <c r="R31" t="n">
-        <v>7008923</v>
+        <v>7008967</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4361,39 +4390,23 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4411,42 +4424,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811914</v>
+        <v>132811949</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4458,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521257</v>
+        <v>521297</v>
       </c>
       <c r="R32" t="n">
-        <v>7008967</v>
+        <v>7009058</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4498,7 +4519,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4507,12 +4528,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4646,65 +4668,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811949</v>
+        <v>132811924</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>80466</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521297</v>
+        <v>521413</v>
       </c>
       <c r="R34" t="n">
-        <v>7009058</v>
+        <v>7008949</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4739,11 +4744,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840111</v>
+        <v>132840108</v>
       </c>
       <c r="B42" t="n">
-        <v>78345</v>
+        <v>91918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521478</v>
+        <v>521417</v>
       </c>
       <c r="R42" t="n">
-        <v>7008952</v>
+        <v>7008986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132840108</v>
+        <v>132840111</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>78345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521417</v>
+        <v>521478</v>
       </c>
       <c r="R43" t="n">
-        <v>7008986</v>
+        <v>7008952</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132840120</v>
+        <v>132840106</v>
       </c>
       <c r="B44" t="n">
-        <v>80304</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521467</v>
+        <v>521412</v>
       </c>
       <c r="R44" t="n">
-        <v>7008865</v>
+        <v>7008994</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132840106</v>
+        <v>132840120</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>80304</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521412</v>
+        <v>521467</v>
       </c>
       <c r="R46" t="n">
-        <v>7008994</v>
+        <v>7008865</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6165,32 +6165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132840124</v>
+        <v>132840113</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521308</v>
+        <v>521480</v>
       </c>
       <c r="R48" t="n">
-        <v>7008922</v>
+        <v>7008948</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6272,7 +6272,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132840091</v>
+        <v>132840124</v>
       </c>
       <c r="B49" t="n">
         <v>79333</v>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521310</v>
+        <v>521308</v>
       </c>
       <c r="R49" t="n">
-        <v>7009002</v>
+        <v>7008922</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6363,21 +6363,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6394,32 +6379,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132840113</v>
+        <v>132840091</v>
       </c>
       <c r="B50" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6429,10 +6414,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521480</v>
+        <v>521310</v>
       </c>
       <c r="R50" t="n">
-        <v>7008948</v>
+        <v>7009002</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6464,7 +6449,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6474,7 +6459,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6485,6 +6470,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132840100</v>
+        <v>132840092</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>91971</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521390</v>
+        <v>521309</v>
       </c>
       <c r="R52" t="n">
-        <v>7009025</v>
+        <v>7008998</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,6 +6699,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6715,10 +6730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132840092</v>
+        <v>132840100</v>
       </c>
       <c r="B53" t="n">
-        <v>91971</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6726,21 +6741,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6750,10 +6765,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521309</v>
+        <v>521390</v>
       </c>
       <c r="R53" t="n">
-        <v>7008998</v>
+        <v>7009025</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6785,7 +6800,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6795,7 +6810,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6806,21 +6821,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840099</v>
+        <v>132840126</v>
       </c>
       <c r="B58" t="n">
-        <v>92217</v>
+        <v>79923</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521388</v>
+        <v>521285</v>
       </c>
       <c r="R58" t="n">
-        <v>7009026</v>
+        <v>7008886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132840126</v>
+        <v>132840123</v>
       </c>
       <c r="B59" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7403,21 +7403,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521285</v>
+        <v>521310</v>
       </c>
       <c r="R59" t="n">
-        <v>7008886</v>
+        <v>7008918</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840123</v>
+        <v>132840099</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>92217</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521310</v>
+        <v>521388</v>
       </c>
       <c r="R60" t="n">
-        <v>7008918</v>
+        <v>7009026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7606,10 +7606,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132840096</v>
+        <v>132840098</v>
       </c>
       <c r="B61" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521376</v>
+        <v>521390</v>
       </c>
       <c r="R61" t="n">
-        <v>7009026</v>
+        <v>7009005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7713,10 +7713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132840098</v>
+        <v>132840096</v>
       </c>
       <c r="B62" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7724,21 +7724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521390</v>
+        <v>521376</v>
       </c>
       <c r="R62" t="n">
-        <v>7009005</v>
+        <v>7009026</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8154,45 +8154,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934683</v>
+        <v>132934540</v>
       </c>
       <c r="B66" t="n">
-        <v>92092</v>
+        <v>79090</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521412</v>
+        <v>521347</v>
       </c>
       <c r="R66" t="n">
-        <v>7008950</v>
+        <v>7008990</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934540</v>
+        <v>132934556</v>
       </c>
       <c r="B67" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521347</v>
+        <v>521357</v>
       </c>
       <c r="R67" t="n">
-        <v>7008990</v>
+        <v>7008968</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,6 +8322,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8348,10 +8353,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934556</v>
+        <v>132934639</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,34 +8364,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521357</v>
+        <v>521297</v>
       </c>
       <c r="R68" t="n">
-        <v>7008968</v>
+        <v>7009054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8419,11 +8424,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8450,32 +8450,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934639</v>
+        <v>132934683</v>
       </c>
       <c r="B69" t="n">
-        <v>80438</v>
+        <v>92092</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521297</v>
+        <v>521412</v>
       </c>
       <c r="R69" t="n">
-        <v>7009054</v>
+        <v>7008950</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8741,32 +8741,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934713</v>
+        <v>132934635</v>
       </c>
       <c r="B72" t="n">
-        <v>92192</v>
+        <v>80438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521238</v>
+        <v>521346</v>
       </c>
       <c r="R72" t="n">
-        <v>7008997</v>
+        <v>7008992</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8838,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934635</v>
+        <v>132934708</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521346</v>
+        <v>521276</v>
       </c>
       <c r="R73" t="n">
-        <v>7008992</v>
+        <v>7009057</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934708</v>
+        <v>132934538</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8946,34 +8946,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521276</v>
+        <v>521314</v>
       </c>
       <c r="R74" t="n">
-        <v>7009057</v>
+        <v>7008997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9032,10 +9032,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934538</v>
+        <v>132934617</v>
       </c>
       <c r="B75" t="n">
-        <v>79090</v>
+        <v>91971</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9043,34 +9043,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521314</v>
+        <v>521420</v>
       </c>
       <c r="R75" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934617</v>
+        <v>132934713</v>
       </c>
       <c r="B76" t="n">
-        <v>91971</v>
+        <v>92192</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521420</v>
+        <v>521238</v>
       </c>
       <c r="R76" t="n">
-        <v>7008863</v>
+        <v>7008997</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9323,45 +9323,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934553</v>
+        <v>132934696</v>
       </c>
       <c r="B78" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521348</v>
+        <v>521297</v>
       </c>
       <c r="R78" t="n">
-        <v>7008988</v>
+        <v>7009003</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9420,32 +9420,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934696</v>
+        <v>132934650</v>
       </c>
       <c r="B79" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9455,10 +9455,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521297</v>
+        <v>521384</v>
       </c>
       <c r="R79" t="n">
-        <v>7009003</v>
+        <v>7009026</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9517,45 +9517,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934650</v>
+        <v>132934553</v>
       </c>
       <c r="B80" t="n">
-        <v>80398</v>
+        <v>92092</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>1503</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521384</v>
+        <v>521348</v>
       </c>
       <c r="R80" t="n">
-        <v>7009026</v>
+        <v>7008988</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9582,12 +9582,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9614,32 +9614,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934563</v>
+        <v>132934721</v>
       </c>
       <c r="B81" t="n">
-        <v>97370</v>
+        <v>93206</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521415</v>
+        <v>521464</v>
       </c>
       <c r="R81" t="n">
-        <v>7008980</v>
+        <v>7008859</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934688</v>
+        <v>132934707</v>
       </c>
       <c r="B83" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521335</v>
+        <v>521289</v>
       </c>
       <c r="R83" t="n">
-        <v>7009020</v>
+        <v>7008957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934707</v>
+        <v>132934688</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521289</v>
+        <v>521335</v>
       </c>
       <c r="R84" t="n">
-        <v>7008957</v>
+        <v>7009020</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9970,12 +9970,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10002,32 +10002,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934721</v>
+        <v>132934563</v>
       </c>
       <c r="B85" t="n">
-        <v>93206</v>
+        <v>97370</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521464</v>
+        <v>521415</v>
       </c>
       <c r="R85" t="n">
-        <v>7008859</v>
+        <v>7008980</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10584,32 +10584,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934711</v>
+        <v>132934657</v>
       </c>
       <c r="B91" t="n">
-        <v>92192</v>
+        <v>80398</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>65</v>
+        <v>229497</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521269</v>
+        <v>521311</v>
       </c>
       <c r="R91" t="n">
-        <v>7008900</v>
+        <v>7009049</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,10 +10681,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934508</v>
+        <v>132934661</v>
       </c>
       <c r="B92" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,34 +10692,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521332</v>
+        <v>521456</v>
       </c>
       <c r="R92" t="n">
-        <v>7009041</v>
+        <v>7008920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10746,12 +10746,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10778,10 +10778,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934661</v>
+        <v>132934705</v>
       </c>
       <c r="B93" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10789,21 +10789,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521456</v>
+        <v>521416</v>
       </c>
       <c r="R93" t="n">
-        <v>7008920</v>
+        <v>7008940</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10875,7 +10875,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934705</v>
+        <v>132934699</v>
       </c>
       <c r="B94" t="n">
         <v>79333</v>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521416</v>
+        <v>521371</v>
       </c>
       <c r="R94" t="n">
-        <v>7008940</v>
+        <v>7009040</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10972,10 +10972,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934699</v>
+        <v>132934508</v>
       </c>
       <c r="B95" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10983,34 +10983,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521371</v>
+        <v>521332</v>
       </c>
       <c r="R95" t="n">
-        <v>7009040</v>
+        <v>7009041</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11069,32 +11069,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934723</v>
+        <v>132934711</v>
       </c>
       <c r="B96" t="n">
-        <v>93206</v>
+        <v>92192</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11104,10 +11104,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521262</v>
+        <v>521269</v>
       </c>
       <c r="R96" t="n">
-        <v>7009041</v>
+        <v>7008900</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11166,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934668</v>
+        <v>132934723</v>
       </c>
       <c r="B97" t="n">
-        <v>99130</v>
+        <v>93206</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521460</v>
+        <v>521262</v>
       </c>
       <c r="R97" t="n">
-        <v>7008862</v>
+        <v>7009041</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11237,11 +11237,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11268,32 +11263,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934657</v>
+        <v>132934668</v>
       </c>
       <c r="B98" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11303,10 +11298,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521311</v>
+        <v>521460</v>
       </c>
       <c r="R98" t="n">
-        <v>7009049</v>
+        <v>7008862</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11333,12 +11328,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11365,45 +11365,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934505</v>
+        <v>132934603</v>
       </c>
       <c r="B99" t="n">
-        <v>97370</v>
+        <v>80342</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521304</v>
+        <v>521339</v>
       </c>
       <c r="R99" t="n">
-        <v>7009055</v>
+        <v>7009060</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11559,45 +11559,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934603</v>
+        <v>132934505</v>
       </c>
       <c r="B101" t="n">
-        <v>80342</v>
+        <v>97370</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521339</v>
+        <v>521304</v>
       </c>
       <c r="R101" t="n">
-        <v>7009060</v>
+        <v>7009055</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11947,32 +11947,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B105" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R105" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,6 +12018,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12141,32 +12146,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B107" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12176,10 +12181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R107" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12212,11 +12217,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12345,32 +12345,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934712</v>
+        <v>132934715</v>
       </c>
       <c r="B109" t="n">
-        <v>92192</v>
+        <v>78999</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12380,10 +12380,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521471</v>
+        <v>521370</v>
       </c>
       <c r="R109" t="n">
-        <v>7008872</v>
+        <v>7008865</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12442,32 +12442,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934715</v>
+        <v>132934712</v>
       </c>
       <c r="B110" t="n">
-        <v>78999</v>
+        <v>92192</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12477,10 +12477,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521370</v>
+        <v>521471</v>
       </c>
       <c r="R110" t="n">
-        <v>7008865</v>
+        <v>7008872</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12738,10 +12738,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934717</v>
+        <v>132934732</v>
       </c>
       <c r="B113" t="n">
-        <v>78999</v>
+        <v>78736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12749,21 +12749,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521268</v>
+        <v>521236</v>
       </c>
       <c r="R113" t="n">
-        <v>7008957</v>
+        <v>7009004</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12835,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934584</v>
+        <v>132934518</v>
       </c>
       <c r="B114" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12846,34 +12846,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521471</v>
+        <v>521253</v>
       </c>
       <c r="R114" t="n">
-        <v>7008946</v>
+        <v>7009010</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12932,32 +12932,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934689</v>
+        <v>132934717</v>
       </c>
       <c r="B115" t="n">
-        <v>92092</v>
+        <v>78999</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521289</v>
+        <v>521268</v>
       </c>
       <c r="R115" t="n">
-        <v>7009060</v>
+        <v>7008957</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,12 +12997,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934732</v>
+        <v>132934584</v>
       </c>
       <c r="B116" t="n">
-        <v>78736</v>
+        <v>91918</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,21 +13040,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521236</v>
+        <v>521471</v>
       </c>
       <c r="R116" t="n">
-        <v>7009004</v>
+        <v>7008946</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13126,45 +13126,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934518</v>
+        <v>132934689</v>
       </c>
       <c r="B117" t="n">
-        <v>79091</v>
+        <v>92092</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521253</v>
+        <v>521289</v>
       </c>
       <c r="R117" t="n">
-        <v>7009010</v>
+        <v>7009060</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934731</v>
+        <v>132934622</v>
       </c>
       <c r="B124" t="n">
-        <v>78340</v>
+        <v>79091</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521235</v>
+        <v>521453</v>
       </c>
       <c r="R124" t="n">
-        <v>7009006</v>
+        <v>7008881</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934622</v>
+        <v>132934731</v>
       </c>
       <c r="B125" t="n">
-        <v>79091</v>
+        <v>78340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521453</v>
+        <v>521235</v>
       </c>
       <c r="R125" t="n">
-        <v>7008881</v>
+        <v>7009006</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14193,32 +14193,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934719</v>
+        <v>132934722</v>
       </c>
       <c r="B128" t="n">
-        <v>78999</v>
+        <v>93206</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521236</v>
+        <v>521256</v>
       </c>
       <c r="R128" t="n">
-        <v>7009013</v>
+        <v>7009005</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14290,10 +14290,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132934718</v>
+        <v>132934581</v>
       </c>
       <c r="B129" t="n">
-        <v>78999</v>
+        <v>79923</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14301,21 +14301,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14325,10 +14325,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>521260</v>
+        <v>521230</v>
       </c>
       <c r="R129" t="n">
-        <v>7008980</v>
+        <v>7009003</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,32 +14387,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132934687</v>
+        <v>132934659</v>
       </c>
       <c r="B130" t="n">
-        <v>92092</v>
+        <v>80398</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1503</v>
+        <v>229497</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14422,10 +14422,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>521353</v>
+        <v>521290</v>
       </c>
       <c r="R130" t="n">
-        <v>7008975</v>
+        <v>7009063</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14484,32 +14484,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132934722</v>
+        <v>132934718</v>
       </c>
       <c r="B131" t="n">
-        <v>93206</v>
+        <v>78999</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>521256</v>
+        <v>521260</v>
       </c>
       <c r="R131" t="n">
-        <v>7009005</v>
+        <v>7008980</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14581,32 +14581,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132934659</v>
+        <v>132934719</v>
       </c>
       <c r="B132" t="n">
-        <v>80398</v>
+        <v>78999</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14616,10 +14616,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>521290</v>
+        <v>521236</v>
       </c>
       <c r="R132" t="n">
-        <v>7009063</v>
+        <v>7009013</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14646,12 +14646,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14678,32 +14678,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132934581</v>
+        <v>132934687</v>
       </c>
       <c r="B133" t="n">
-        <v>79923</v>
+        <v>92092</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>521230</v>
+        <v>521353</v>
       </c>
       <c r="R133" t="n">
-        <v>7009003</v>
+        <v>7008975</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14743,12 +14743,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14969,32 +14969,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132934686</v>
+        <v>132934714</v>
       </c>
       <c r="B136" t="n">
-        <v>92092</v>
+        <v>78999</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15004,10 +15004,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>521364</v>
+        <v>521381</v>
       </c>
       <c r="R136" t="n">
-        <v>7008948</v>
+        <v>7008904</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15066,45 +15066,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132934519</v>
+        <v>132934686</v>
       </c>
       <c r="B137" t="n">
-        <v>79091</v>
+        <v>92092</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>521418</v>
+        <v>521364</v>
       </c>
       <c r="R137" t="n">
-        <v>7008891</v>
+        <v>7008948</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15163,10 +15163,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132934579</v>
+        <v>132934519</v>
       </c>
       <c r="B138" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15174,34 +15174,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>521343</v>
+        <v>521418</v>
       </c>
       <c r="R138" t="n">
-        <v>7008898</v>
+        <v>7008891</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15228,12 +15228,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15260,10 +15260,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132934714</v>
+        <v>132934579</v>
       </c>
       <c r="B139" t="n">
-        <v>78999</v>
+        <v>79923</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15271,21 +15271,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>521381</v>
+        <v>521343</v>
       </c>
       <c r="R139" t="n">
-        <v>7008904</v>
+        <v>7008898</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15556,32 +15556,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934653</v>
+        <v>132934636</v>
       </c>
       <c r="B142" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15591,10 +15591,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521357</v>
+        <v>521362</v>
       </c>
       <c r="R142" t="n">
-        <v>7009035</v>
+        <v>7009037</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934536</v>
+        <v>132934537</v>
       </c>
       <c r="B143" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15688,10 +15688,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521324</v>
+        <v>521253</v>
       </c>
       <c r="R143" t="n">
-        <v>7009052</v>
+        <v>7009010</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15750,45 +15750,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934509</v>
+        <v>132934648</v>
       </c>
       <c r="B144" t="n">
-        <v>91918</v>
+        <v>80305</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>385</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521329</v>
+        <v>521468</v>
       </c>
       <c r="R144" t="n">
-        <v>7009049</v>
+        <v>7008870</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15815,12 +15815,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15829,6 +15829,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15847,45 +15848,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132934648</v>
+        <v>132934509</v>
       </c>
       <c r="B145" t="n">
-        <v>80305</v>
+        <v>91918</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>385</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>521468</v>
+        <v>521329</v>
       </c>
       <c r="R145" t="n">
-        <v>7008870</v>
+        <v>7009049</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15912,12 +15913,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15926,7 +15927,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15945,10 +15945,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132934636</v>
+        <v>132934561</v>
       </c>
       <c r="B146" t="n">
-        <v>80438</v>
+        <v>91840</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>3242</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>521362</v>
+        <v>521263</v>
       </c>
       <c r="R146" t="n">
-        <v>7009037</v>
+        <v>7008978</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16010,12 +16010,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16042,45 +16042,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>132934537</v>
+        <v>132934653</v>
       </c>
       <c r="B147" t="n">
-        <v>79090</v>
+        <v>80398</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>521253</v>
+        <v>521357</v>
       </c>
       <c r="R147" t="n">
-        <v>7009010</v>
+        <v>7009035</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16139,45 +16139,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132934561</v>
+        <v>132934536</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>80398</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>3242</v>
+        <v>229497</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>521263</v>
+        <v>521324</v>
       </c>
       <c r="R148" t="n">
-        <v>7008978</v>
+        <v>7009052</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16204,12 +16204,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD148" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -3549,7 +3549,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132811907</v>
+        <v>132811905</v>
       </c>
       <c r="B25" t="n">
         <v>91918</v>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521299</v>
+        <v>521413</v>
       </c>
       <c r="R25" t="n">
-        <v>7009060</v>
+        <v>7008997</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,7 +3641,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Med fuktstråk.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3656,12 +3661,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3679,7 +3684,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132811905</v>
+        <v>132811907</v>
       </c>
       <c r="B26" t="n">
         <v>91918</v>
@@ -3721,10 +3726,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521413</v>
+        <v>521299</v>
       </c>
       <c r="R26" t="n">
-        <v>7008997</v>
+        <v>7009060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3771,12 +3776,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Med fuktstråk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4424,65 +4424,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811949</v>
+        <v>132811924</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>80466</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521297</v>
+        <v>521413</v>
       </c>
       <c r="R32" t="n">
-        <v>7009058</v>
+        <v>7008949</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4517,11 +4500,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4534,7 +4512,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4552,53 +4530,65 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811988</v>
+        <v>132811949</v>
       </c>
       <c r="B33" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521434</v>
+        <v>521297</v>
       </c>
       <c r="R33" t="n">
-        <v>7008976</v>
+        <v>7009058</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4635,7 +4625,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4668,10 +4658,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811924</v>
+        <v>132811988</v>
       </c>
       <c r="B34" t="n">
-        <v>80466</v>
+        <v>101338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4679,26 +4669,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4706,10 +4701,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521413</v>
+        <v>521434</v>
       </c>
       <c r="R34" t="n">
-        <v>7008949</v>
+        <v>7008976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4744,6 +4739,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132840103</v>
+        <v>132840111</v>
       </c>
       <c r="B41" t="n">
-        <v>83315</v>
+        <v>78345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521403</v>
+        <v>521478</v>
       </c>
       <c r="R41" t="n">
-        <v>7008996</v>
+        <v>7008952</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840108</v>
+        <v>132840103</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521417</v>
+        <v>521403</v>
       </c>
       <c r="R42" t="n">
-        <v>7008986</v>
+        <v>7008996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132840111</v>
+        <v>132840108</v>
       </c>
       <c r="B43" t="n">
-        <v>78345</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521478</v>
+        <v>521417</v>
       </c>
       <c r="R43" t="n">
-        <v>7008952</v>
+        <v>7008986</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5737,10 +5737,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132840106</v>
+        <v>132840120</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>80304</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521412</v>
+        <v>521467</v>
       </c>
       <c r="R44" t="n">
-        <v>7008994</v>
+        <v>7008865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132840110</v>
+        <v>132840106</v>
       </c>
       <c r="B45" t="n">
-        <v>83315</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521479</v>
+        <v>521412</v>
       </c>
       <c r="R45" t="n">
-        <v>7008951</v>
+        <v>7008994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132840120</v>
+        <v>132840110</v>
       </c>
       <c r="B46" t="n">
-        <v>80304</v>
+        <v>83315</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>388</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521467</v>
+        <v>521479</v>
       </c>
       <c r="R46" t="n">
-        <v>7008865</v>
+        <v>7008951</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -8935,10 +8935,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934538</v>
+        <v>132934617</v>
       </c>
       <c r="B74" t="n">
-        <v>79090</v>
+        <v>91971</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8946,34 +8946,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521314</v>
+        <v>521420</v>
       </c>
       <c r="R74" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9032,32 +9032,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934617</v>
+        <v>132934713</v>
       </c>
       <c r="B75" t="n">
-        <v>91971</v>
+        <v>92192</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521420</v>
+        <v>521238</v>
       </c>
       <c r="R75" t="n">
-        <v>7008863</v>
+        <v>7008997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934713</v>
+        <v>132934656</v>
       </c>
       <c r="B76" t="n">
-        <v>92192</v>
+        <v>80398</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521238</v>
+        <v>521300</v>
       </c>
       <c r="R76" t="n">
-        <v>7008997</v>
+        <v>7009071</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9226,45 +9226,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934656</v>
+        <v>132934538</v>
       </c>
       <c r="B77" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521300</v>
+        <v>521314</v>
       </c>
       <c r="R77" t="n">
-        <v>7009071</v>
+        <v>7008997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9614,32 +9614,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934721</v>
+        <v>132934688</v>
       </c>
       <c r="B81" t="n">
-        <v>93206</v>
+        <v>92092</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521464</v>
+        <v>521335</v>
       </c>
       <c r="R81" t="n">
-        <v>7008859</v>
+        <v>7009020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9711,10 +9711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934706</v>
+        <v>132934563</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>97370</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521426</v>
+        <v>521415</v>
       </c>
       <c r="R82" t="n">
-        <v>7008976</v>
+        <v>7008980</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934707</v>
+        <v>132934721</v>
       </c>
       <c r="B83" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521289</v>
+        <v>521464</v>
       </c>
       <c r="R83" t="n">
-        <v>7008957</v>
+        <v>7008859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934688</v>
+        <v>132934706</v>
       </c>
       <c r="B84" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521335</v>
+        <v>521426</v>
       </c>
       <c r="R84" t="n">
-        <v>7009020</v>
+        <v>7008976</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9970,12 +9970,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10002,10 +10002,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934563</v>
+        <v>132934707</v>
       </c>
       <c r="B85" t="n">
-        <v>97370</v>
+        <v>79333</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10013,21 +10013,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521415</v>
+        <v>521289</v>
       </c>
       <c r="R85" t="n">
-        <v>7008980</v>
+        <v>7008957</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10584,32 +10584,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934657</v>
+        <v>132934661</v>
       </c>
       <c r="B91" t="n">
-        <v>80398</v>
+        <v>79090</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521311</v>
+        <v>521456</v>
       </c>
       <c r="R91" t="n">
-        <v>7009049</v>
+        <v>7008920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,10 +10681,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934661</v>
+        <v>132934705</v>
       </c>
       <c r="B92" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10692,21 +10692,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521456</v>
+        <v>521416</v>
       </c>
       <c r="R92" t="n">
-        <v>7008920</v>
+        <v>7008940</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10778,7 +10778,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934705</v>
+        <v>132934699</v>
       </c>
       <c r="B93" t="n">
         <v>79333</v>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521416</v>
+        <v>521371</v>
       </c>
       <c r="R93" t="n">
-        <v>7008940</v>
+        <v>7009040</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10843,12 +10843,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10875,10 +10875,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934699</v>
+        <v>132934508</v>
       </c>
       <c r="B94" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10886,34 +10886,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521371</v>
+        <v>521332</v>
       </c>
       <c r="R94" t="n">
-        <v>7009040</v>
+        <v>7009041</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10972,45 +10972,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934508</v>
+        <v>132934711</v>
       </c>
       <c r="B95" t="n">
-        <v>91918</v>
+        <v>92192</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>65</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521332</v>
+        <v>521269</v>
       </c>
       <c r="R95" t="n">
-        <v>7009041</v>
+        <v>7008900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11069,32 +11069,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934711</v>
+        <v>132934723</v>
       </c>
       <c r="B96" t="n">
-        <v>92192</v>
+        <v>93206</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11104,10 +11104,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521269</v>
+        <v>521262</v>
       </c>
       <c r="R96" t="n">
-        <v>7008900</v>
+        <v>7009041</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11166,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934723</v>
+        <v>132934668</v>
       </c>
       <c r="B97" t="n">
-        <v>93206</v>
+        <v>99130</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521262</v>
+        <v>521460</v>
       </c>
       <c r="R97" t="n">
-        <v>7009041</v>
+        <v>7008862</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11237,6 +11237,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11263,32 +11268,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934668</v>
+        <v>132934657</v>
       </c>
       <c r="B98" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11298,10 +11303,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521460</v>
+        <v>521311</v>
       </c>
       <c r="R98" t="n">
-        <v>7008862</v>
+        <v>7009049</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11328,17 +11333,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11947,32 +11947,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934669</v>
+        <v>132934643</v>
       </c>
       <c r="B105" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521481</v>
+        <v>521368</v>
       </c>
       <c r="R105" t="n">
-        <v>7008912</v>
+        <v>7009037</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,11 +12018,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12049,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934643</v>
+        <v>132934669</v>
       </c>
       <c r="B106" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12084,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521368</v>
+        <v>521481</v>
       </c>
       <c r="R106" t="n">
-        <v>7009037</v>
+        <v>7008912</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12120,6 +12115,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12738,10 +12738,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934732</v>
+        <v>132934518</v>
       </c>
       <c r="B113" t="n">
-        <v>78736</v>
+        <v>79091</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12749,34 +12749,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521236</v>
+        <v>521253</v>
       </c>
       <c r="R113" t="n">
-        <v>7009004</v>
+        <v>7009010</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12803,12 +12803,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12835,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934518</v>
+        <v>132934732</v>
       </c>
       <c r="B114" t="n">
-        <v>79091</v>
+        <v>78736</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12846,34 +12846,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521253</v>
+        <v>521236</v>
       </c>
       <c r="R114" t="n">
-        <v>7009010</v>
+        <v>7009004</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R2" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,26 +764,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B3" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R3" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +857,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,6 +875,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1023,65 +1023,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132811946</v>
+        <v>132811986</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521337</v>
+        <v>521479</v>
       </c>
       <c r="R5" t="n">
-        <v>7009020</v>
+        <v>7008956</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,11 +1104,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 1 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1133,7 +1116,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,53 +1134,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132811986</v>
+        <v>132811946</v>
       </c>
       <c r="B6" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521479</v>
+        <v>521337</v>
       </c>
       <c r="R6" t="n">
-        <v>7008956</v>
+        <v>7009020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,6 +1227,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 1 m2 yta i tallskog.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1626,42 +1626,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132811916</v>
+        <v>132811932</v>
       </c>
       <c r="B10" t="n">
-        <v>104642</v>
+        <v>80438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521428</v>
+        <v>521288</v>
       </c>
       <c r="R10" t="n">
-        <v>7008979</v>
+        <v>7008966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,11 +1706,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,7 +1718,32 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En högstubbe.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula # En högstubbe.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1742,41 +1761,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132811932</v>
+        <v>132811916</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>104642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521288</v>
+        <v>521428</v>
       </c>
       <c r="R11" t="n">
-        <v>7008966</v>
+        <v>7008979</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,6 +1842,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1834,32 +1859,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En högstubbe.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula # En högstubbe.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2655,48 +2655,65 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132811929</v>
+        <v>132811944</v>
       </c>
       <c r="B18" t="n">
-        <v>79091</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521300</v>
+        <v>521377</v>
       </c>
       <c r="R18" t="n">
-        <v>7009023</v>
+        <v>7009007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2733,7 +2750,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad tallved i tallskog.</t>
+          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2749,26 +2766,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Branddödat träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2786,10 +2783,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811902</v>
+        <v>132811929</v>
       </c>
       <c r="B19" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2797,21 +2794,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2824,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521234</v>
+        <v>521300</v>
       </c>
       <c r="R19" t="n">
-        <v>7008999</v>
+        <v>7009023</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2862,6 +2859,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad tallved i tallskog.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2874,7 +2876,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2889,12 +2891,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2912,10 +2914,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811968</v>
+        <v>132811902</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2923,21 +2925,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2950,10 +2952,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521278</v>
+        <v>521234</v>
       </c>
       <c r="R20" t="n">
-        <v>7009051</v>
+        <v>7008999</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3000,7 +3002,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3015,12 +3017,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3038,7 +3040,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811970</v>
+        <v>132811968</v>
       </c>
       <c r="B21" t="n">
         <v>79333</v>
@@ -3076,10 +3078,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521326</v>
+        <v>521278</v>
       </c>
       <c r="R21" t="n">
-        <v>7008987</v>
+        <v>7009051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3164,65 +3166,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811944</v>
+        <v>132811970</v>
       </c>
       <c r="B22" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521377</v>
+        <v>521326</v>
       </c>
       <c r="R22" t="n">
-        <v>7009007</v>
+        <v>7008987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3257,11 +3242,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 80 plantor inom ca 1,5 m2 yta i tallskog.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3275,6 +3255,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132811905</v>
+        <v>132811907</v>
       </c>
       <c r="B25" t="n">
         <v>91918</v>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521413</v>
+        <v>521299</v>
       </c>
       <c r="R25" t="n">
-        <v>7008997</v>
+        <v>7009060</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,12 +3641,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Med fuktstråk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3661,12 +3656,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3684,7 +3679,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132811907</v>
+        <v>132811905</v>
       </c>
       <c r="B26" t="n">
         <v>91918</v>
@@ -3726,10 +3721,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521299</v>
+        <v>521413</v>
       </c>
       <c r="R26" t="n">
-        <v>7009060</v>
+        <v>7008997</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3776,7 +3771,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Med fuktstråk.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3940,65 +3940,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132811948</v>
+        <v>132811984</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521326</v>
+        <v>521469</v>
       </c>
       <c r="R28" t="n">
-        <v>7009043</v>
+        <v>7008936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4033,11 +4021,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 85 plantor inom ca 3 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4050,7 +4033,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4068,53 +4051,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132811984</v>
+        <v>132811948</v>
       </c>
       <c r="B29" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521469</v>
+        <v>521326</v>
       </c>
       <c r="R29" t="n">
-        <v>7008936</v>
+        <v>7009043</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4149,6 +4144,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 85 plantor inom ca 3 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4424,48 +4424,65 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811924</v>
+        <v>132811949</v>
       </c>
       <c r="B32" t="n">
-        <v>80466</v>
+        <v>99130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521413</v>
+        <v>521297</v>
       </c>
       <c r="R32" t="n">
-        <v>7008949</v>
+        <v>7009058</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4500,6 +4517,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4512,7 +4534,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4530,65 +4552,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811949</v>
+        <v>132811924</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>80466</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521297</v>
+        <v>521413</v>
       </c>
       <c r="R33" t="n">
-        <v>7009058</v>
+        <v>7008949</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4623,11 +4628,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5095,32 +5095,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132840095</v>
+        <v>132840125</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>92192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521362</v>
+        <v>521309</v>
       </c>
       <c r="R38" t="n">
-        <v>7009022</v>
+        <v>7008931</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5202,32 +5202,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132840125</v>
+        <v>132840095</v>
       </c>
       <c r="B39" t="n">
-        <v>92192</v>
+        <v>80438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521309</v>
+        <v>521362</v>
       </c>
       <c r="R39" t="n">
-        <v>7008931</v>
+        <v>7009022</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5416,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132840111</v>
+        <v>132840108</v>
       </c>
       <c r="B41" t="n">
-        <v>78345</v>
+        <v>91918</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521478</v>
+        <v>521417</v>
       </c>
       <c r="R41" t="n">
-        <v>7008952</v>
+        <v>7008986</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840103</v>
+        <v>132840111</v>
       </c>
       <c r="B42" t="n">
-        <v>83315</v>
+        <v>78345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521403</v>
+        <v>521478</v>
       </c>
       <c r="R42" t="n">
-        <v>7008996</v>
+        <v>7008952</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132840108</v>
+        <v>132840103</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521417</v>
+        <v>521403</v>
       </c>
       <c r="R43" t="n">
-        <v>7008986</v>
+        <v>7008996</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132840106</v>
+        <v>132840110</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>83315</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521412</v>
+        <v>521479</v>
       </c>
       <c r="R45" t="n">
-        <v>7008994</v>
+        <v>7008951</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132840110</v>
+        <v>132840106</v>
       </c>
       <c r="B46" t="n">
-        <v>83315</v>
+        <v>79333</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5962,21 +5962,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521479</v>
+        <v>521412</v>
       </c>
       <c r="R46" t="n">
-        <v>7008951</v>
+        <v>7008994</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6165,32 +6165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132840113</v>
+        <v>132840124</v>
       </c>
       <c r="B48" t="n">
-        <v>101338</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521480</v>
+        <v>521308</v>
       </c>
       <c r="R48" t="n">
-        <v>7008948</v>
+        <v>7008922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6272,7 +6272,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132840124</v>
+        <v>132840091</v>
       </c>
       <c r="B49" t="n">
         <v>79333</v>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521308</v>
+        <v>521310</v>
       </c>
       <c r="R49" t="n">
-        <v>7008922</v>
+        <v>7009002</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6363,6 +6363,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6379,32 +6394,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132840091</v>
+        <v>132840113</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>101338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6414,10 +6429,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521310</v>
+        <v>521480</v>
       </c>
       <c r="R50" t="n">
-        <v>7009002</v>
+        <v>7008948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6449,7 +6464,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6459,7 +6474,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6470,21 +6485,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132840092</v>
+        <v>132840100</v>
       </c>
       <c r="B52" t="n">
-        <v>91971</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521309</v>
+        <v>521390</v>
       </c>
       <c r="R52" t="n">
-        <v>7008998</v>
+        <v>7009025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,21 +6699,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6730,10 +6715,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132840100</v>
+        <v>132840092</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>91971</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6741,21 +6726,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6765,10 +6750,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521390</v>
+        <v>521309</v>
       </c>
       <c r="R53" t="n">
-        <v>7009025</v>
+        <v>7008998</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6800,7 +6785,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6810,7 +6795,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6821,6 +6806,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840126</v>
+        <v>132840099</v>
       </c>
       <c r="B58" t="n">
-        <v>79923</v>
+        <v>92217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521285</v>
+        <v>521388</v>
       </c>
       <c r="R58" t="n">
-        <v>7008886</v>
+        <v>7009026</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132840123</v>
+        <v>132840126</v>
       </c>
       <c r="B59" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7403,21 +7403,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521310</v>
+        <v>521285</v>
       </c>
       <c r="R59" t="n">
-        <v>7008918</v>
+        <v>7008886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840099</v>
+        <v>132840123</v>
       </c>
       <c r="B60" t="n">
-        <v>92217</v>
+        <v>79091</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521388</v>
+        <v>521310</v>
       </c>
       <c r="R60" t="n">
-        <v>7009026</v>
+        <v>7008918</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8838,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934708</v>
+        <v>132934538</v>
       </c>
       <c r="B73" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8849,34 +8849,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521276</v>
+        <v>521314</v>
       </c>
       <c r="R73" t="n">
-        <v>7009057</v>
+        <v>7008997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934617</v>
+        <v>132934708</v>
       </c>
       <c r="B74" t="n">
-        <v>91971</v>
+        <v>79333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8946,21 +8946,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521420</v>
+        <v>521276</v>
       </c>
       <c r="R74" t="n">
-        <v>7008863</v>
+        <v>7009057</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9032,32 +9032,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934713</v>
+        <v>132934617</v>
       </c>
       <c r="B75" t="n">
-        <v>92192</v>
+        <v>91971</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9067,10 +9067,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521238</v>
+        <v>521420</v>
       </c>
       <c r="R75" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934656</v>
+        <v>132934713</v>
       </c>
       <c r="B76" t="n">
-        <v>80398</v>
+        <v>92192</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521300</v>
+        <v>521238</v>
       </c>
       <c r="R76" t="n">
-        <v>7009071</v>
+        <v>7008997</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9226,45 +9226,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934538</v>
+        <v>132934656</v>
       </c>
       <c r="B77" t="n">
-        <v>79090</v>
+        <v>80398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521314</v>
+        <v>521300</v>
       </c>
       <c r="R77" t="n">
-        <v>7008997</v>
+        <v>7009071</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9323,32 +9323,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934696</v>
+        <v>132934650</v>
       </c>
       <c r="B78" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521297</v>
+        <v>521384</v>
       </c>
       <c r="R78" t="n">
-        <v>7009003</v>
+        <v>7009026</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9420,45 +9420,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934650</v>
+        <v>132934553</v>
       </c>
       <c r="B79" t="n">
-        <v>80398</v>
+        <v>92092</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229497</v>
+        <v>1503</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521384</v>
+        <v>521348</v>
       </c>
       <c r="R79" t="n">
-        <v>7009026</v>
+        <v>7008988</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9517,45 +9517,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934553</v>
+        <v>132934696</v>
       </c>
       <c r="B80" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521348</v>
+        <v>521297</v>
       </c>
       <c r="R80" t="n">
-        <v>7008988</v>
+        <v>7009003</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9582,12 +9582,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9614,32 +9614,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934688</v>
+        <v>132934706</v>
       </c>
       <c r="B81" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521335</v>
+        <v>521426</v>
       </c>
       <c r="R81" t="n">
-        <v>7009020</v>
+        <v>7008976</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9711,10 +9711,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934563</v>
+        <v>132934707</v>
       </c>
       <c r="B82" t="n">
-        <v>97370</v>
+        <v>79333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9722,21 +9722,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521415</v>
+        <v>521289</v>
       </c>
       <c r="R82" t="n">
-        <v>7008980</v>
+        <v>7008957</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934721</v>
+        <v>132934688</v>
       </c>
       <c r="B83" t="n">
-        <v>93206</v>
+        <v>92092</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521464</v>
+        <v>521335</v>
       </c>
       <c r="R83" t="n">
-        <v>7008859</v>
+        <v>7009020</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9905,10 +9905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934706</v>
+        <v>132934563</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>97370</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9916,21 +9916,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521426</v>
+        <v>521415</v>
       </c>
       <c r="R84" t="n">
-        <v>7008976</v>
+        <v>7008980</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,32 +10002,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934707</v>
+        <v>132934721</v>
       </c>
       <c r="B85" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521289</v>
+        <v>521464</v>
       </c>
       <c r="R85" t="n">
-        <v>7008957</v>
+        <v>7008859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10584,10 +10584,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934661</v>
+        <v>132934508</v>
       </c>
       <c r="B91" t="n">
-        <v>79090</v>
+        <v>91918</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10595,34 +10595,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521456</v>
+        <v>521332</v>
       </c>
       <c r="R91" t="n">
-        <v>7008920</v>
+        <v>7009041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,32 +10681,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934705</v>
+        <v>132934711</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>92192</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521416</v>
+        <v>521269</v>
       </c>
       <c r="R92" t="n">
-        <v>7008940</v>
+        <v>7008900</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10778,32 +10778,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934699</v>
+        <v>132934723</v>
       </c>
       <c r="B93" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521371</v>
+        <v>521262</v>
       </c>
       <c r="R93" t="n">
-        <v>7009040</v>
+        <v>7009041</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10843,12 +10843,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10875,45 +10875,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934508</v>
+        <v>132934668</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521332</v>
+        <v>521460</v>
       </c>
       <c r="R94" t="n">
-        <v>7009041</v>
+        <v>7008862</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10940,12 +10940,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10972,32 +10977,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934711</v>
+        <v>132934661</v>
       </c>
       <c r="B95" t="n">
-        <v>92192</v>
+        <v>79090</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521269</v>
+        <v>521456</v>
       </c>
       <c r="R95" t="n">
-        <v>7008900</v>
+        <v>7008920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11069,32 +11074,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934723</v>
+        <v>132934705</v>
       </c>
       <c r="B96" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11104,10 +11109,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521262</v>
+        <v>521416</v>
       </c>
       <c r="R96" t="n">
-        <v>7009041</v>
+        <v>7008940</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11166,32 +11171,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934668</v>
+        <v>132934699</v>
       </c>
       <c r="B97" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11206,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521460</v>
+        <v>521371</v>
       </c>
       <c r="R97" t="n">
-        <v>7008862</v>
+        <v>7009040</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11231,17 +11236,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11462,32 +11462,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934685</v>
+        <v>132934621</v>
       </c>
       <c r="B100" t="n">
-        <v>92092</v>
+        <v>79091</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521278</v>
+        <v>521284</v>
       </c>
       <c r="R100" t="n">
-        <v>7008985</v>
+        <v>7008883</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11559,10 +11559,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934505</v>
+        <v>132934580</v>
       </c>
       <c r="B101" t="n">
-        <v>97370</v>
+        <v>79923</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11570,34 +11570,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521304</v>
+        <v>521256</v>
       </c>
       <c r="R101" t="n">
-        <v>7009055</v>
+        <v>7008979</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11656,7 +11656,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934621</v>
+        <v>132934520</v>
       </c>
       <c r="B102" t="n">
         <v>79091</v>
@@ -11687,14 +11687,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521284</v>
+        <v>521367</v>
       </c>
       <c r="R102" t="n">
-        <v>7008883</v>
+        <v>7008928</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11721,12 +11721,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11753,32 +11753,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934580</v>
+        <v>132934685</v>
       </c>
       <c r="B103" t="n">
-        <v>79923</v>
+        <v>92092</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521256</v>
+        <v>521278</v>
       </c>
       <c r="R103" t="n">
-        <v>7008979</v>
+        <v>7008985</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11850,10 +11850,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934520</v>
+        <v>132934505</v>
       </c>
       <c r="B104" t="n">
-        <v>79091</v>
+        <v>97370</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11861,21 +11861,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11885,10 +11885,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521367</v>
+        <v>521304</v>
       </c>
       <c r="R104" t="n">
-        <v>7008928</v>
+        <v>7009055</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B106" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R106" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,11 +12115,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12146,32 +12141,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B107" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12181,10 +12176,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R107" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12217,6 +12212,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12243,10 +12243,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132934637</v>
+        <v>132934715</v>
       </c>
       <c r="B108" t="n">
-        <v>80438</v>
+        <v>78999</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12254,21 +12254,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>521330</v>
+        <v>521370</v>
       </c>
       <c r="R108" t="n">
-        <v>7009056</v>
+        <v>7008865</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12308,17 +12308,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12345,32 +12340,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934715</v>
+        <v>132934712</v>
       </c>
       <c r="B109" t="n">
-        <v>78999</v>
+        <v>92192</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12380,10 +12375,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521370</v>
+        <v>521471</v>
       </c>
       <c r="R109" t="n">
-        <v>7008865</v>
+        <v>7008872</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12442,32 +12437,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934712</v>
+        <v>132934637</v>
       </c>
       <c r="B110" t="n">
-        <v>92192</v>
+        <v>80438</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12477,10 +12472,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521471</v>
+        <v>521330</v>
       </c>
       <c r="R110" t="n">
-        <v>7008872</v>
+        <v>7009056</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12507,12 +12502,17 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12738,10 +12738,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934518</v>
+        <v>132934717</v>
       </c>
       <c r="B113" t="n">
-        <v>79091</v>
+        <v>78999</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12749,34 +12749,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521253</v>
+        <v>521268</v>
       </c>
       <c r="R113" t="n">
-        <v>7009010</v>
+        <v>7008957</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12803,12 +12803,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12835,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934732</v>
+        <v>132934584</v>
       </c>
       <c r="B114" t="n">
-        <v>78736</v>
+        <v>91918</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12846,21 +12846,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521236</v>
+        <v>521471</v>
       </c>
       <c r="R114" t="n">
-        <v>7009004</v>
+        <v>7008946</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12932,32 +12932,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934717</v>
+        <v>132934689</v>
       </c>
       <c r="B115" t="n">
-        <v>78999</v>
+        <v>92092</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521268</v>
+        <v>521289</v>
       </c>
       <c r="R115" t="n">
-        <v>7008957</v>
+        <v>7009060</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,12 +12997,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934584</v>
+        <v>132934518</v>
       </c>
       <c r="B116" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,34 +13040,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521471</v>
+        <v>521253</v>
       </c>
       <c r="R116" t="n">
-        <v>7008946</v>
+        <v>7009010</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13094,12 +13094,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13126,32 +13126,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934689</v>
+        <v>132934732</v>
       </c>
       <c r="B117" t="n">
-        <v>92092</v>
+        <v>78736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13161,10 +13161,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521289</v>
+        <v>521236</v>
       </c>
       <c r="R117" t="n">
-        <v>7009060</v>
+        <v>7009004</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13191,12 +13191,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13708,32 +13708,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934720</v>
+        <v>132934622</v>
       </c>
       <c r="B123" t="n">
-        <v>93206</v>
+        <v>79091</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521341</v>
+        <v>521453</v>
       </c>
       <c r="R123" t="n">
-        <v>7008936</v>
+        <v>7008881</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,10 +13805,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934622</v>
+        <v>132934731</v>
       </c>
       <c r="B124" t="n">
-        <v>79091</v>
+        <v>78340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13816,21 +13816,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521453</v>
+        <v>521235</v>
       </c>
       <c r="R124" t="n">
-        <v>7008881</v>
+        <v>7009006</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934731</v>
+        <v>132934720</v>
       </c>
       <c r="B125" t="n">
-        <v>78340</v>
+        <v>93206</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521235</v>
+        <v>521341</v>
       </c>
       <c r="R125" t="n">
-        <v>7009006</v>
+        <v>7008936</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14193,10 +14193,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934722</v>
+        <v>132934659</v>
       </c>
       <c r="B128" t="n">
-        <v>93206</v>
+        <v>80398</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14204,21 +14204,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521256</v>
+        <v>521290</v>
       </c>
       <c r="R128" t="n">
-        <v>7009005</v>
+        <v>7009063</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14258,12 +14258,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14387,32 +14387,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132934659</v>
+        <v>132934718</v>
       </c>
       <c r="B130" t="n">
-        <v>80398</v>
+        <v>78999</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14422,10 +14422,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>521290</v>
+        <v>521260</v>
       </c>
       <c r="R130" t="n">
-        <v>7009063</v>
+        <v>7008980</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14452,12 +14452,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14484,7 +14484,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132934718</v>
+        <v>132934719</v>
       </c>
       <c r="B131" t="n">
         <v>78999</v>
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>521260</v>
+        <v>521236</v>
       </c>
       <c r="R131" t="n">
-        <v>7008980</v>
+        <v>7009013</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14581,32 +14581,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132934719</v>
+        <v>132934687</v>
       </c>
       <c r="B132" t="n">
-        <v>78999</v>
+        <v>92092</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14616,10 +14616,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>521236</v>
+        <v>521353</v>
       </c>
       <c r="R132" t="n">
-        <v>7009013</v>
+        <v>7008975</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14646,12 +14646,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14678,32 +14678,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132934687</v>
+        <v>132934722</v>
       </c>
       <c r="B133" t="n">
-        <v>92092</v>
+        <v>93206</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>521353</v>
+        <v>521256</v>
       </c>
       <c r="R133" t="n">
-        <v>7008975</v>
+        <v>7009005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14743,12 +14743,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15357,32 +15357,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132934652</v>
+        <v>132934636</v>
       </c>
       <c r="B140" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>521312</v>
+        <v>521362</v>
       </c>
       <c r="R140" t="n">
-        <v>7009003</v>
+        <v>7009037</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15422,17 +15422,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Med apotechier</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15459,10 +15454,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132934578</v>
+        <v>132934537</v>
       </c>
       <c r="B141" t="n">
-        <v>79923</v>
+        <v>79090</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15470,34 +15465,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>521336</v>
+        <v>521253</v>
       </c>
       <c r="R141" t="n">
-        <v>7008869</v>
+        <v>7009010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15524,12 +15519,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15556,32 +15551,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934636</v>
+        <v>132934648</v>
       </c>
       <c r="B142" t="n">
-        <v>80438</v>
+        <v>80305</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15591,10 +15586,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521362</v>
+        <v>521468</v>
       </c>
       <c r="R142" t="n">
-        <v>7009037</v>
+        <v>7008870</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15621,12 +15616,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15635,6 +15630,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15653,10 +15649,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934537</v>
+        <v>132934509</v>
       </c>
       <c r="B143" t="n">
-        <v>79090</v>
+        <v>91918</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15664,21 +15660,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15688,10 +15684,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521253</v>
+        <v>521329</v>
       </c>
       <c r="R143" t="n">
-        <v>7009010</v>
+        <v>7009049</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15750,32 +15746,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934648</v>
+        <v>132934561</v>
       </c>
       <c r="B144" t="n">
-        <v>80305</v>
+        <v>91840</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>385</v>
+        <v>3242</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15785,10 +15781,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521468</v>
+        <v>521263</v>
       </c>
       <c r="R144" t="n">
-        <v>7008870</v>
+        <v>7008978</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15829,7 +15825,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15848,45 +15843,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132934509</v>
+        <v>132934652</v>
       </c>
       <c r="B145" t="n">
-        <v>91918</v>
+        <v>80398</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>521329</v>
+        <v>521312</v>
       </c>
       <c r="R145" t="n">
-        <v>7009049</v>
+        <v>7009003</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15913,12 +15908,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Med apotechier</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15945,10 +15945,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132934561</v>
+        <v>132934578</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>79923</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3242</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>521263</v>
+        <v>521336</v>
       </c>
       <c r="R146" t="n">
-        <v>7008978</v>
+        <v>7008869</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R2" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,32 +806,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R3" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +882,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,26 +895,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2265,48 +2265,65 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132811972</v>
+        <v>132811943</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521260</v>
+        <v>521374</v>
       </c>
       <c r="R15" t="n">
-        <v>7008973</v>
+        <v>7008999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2343,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,27 +2375,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2396,65 +2393,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132811943</v>
+        <v>132811972</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521374</v>
+        <v>521260</v>
       </c>
       <c r="R16" t="n">
-        <v>7008999</v>
+        <v>7008973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2471,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
+          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,7 +2486,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811929</v>
+        <v>132811968</v>
       </c>
       <c r="B19" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2794,21 +2794,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521300</v>
+        <v>521278</v>
       </c>
       <c r="R19" t="n">
-        <v>7009023</v>
+        <v>7009051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2859,11 +2859,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad tallved i tallskog.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2891,12 +2886,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2914,10 +2909,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811902</v>
+        <v>132811970</v>
       </c>
       <c r="B20" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,21 +2920,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521234</v>
+        <v>521326</v>
       </c>
       <c r="R20" t="n">
-        <v>7008999</v>
+        <v>7008987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3002,7 +2997,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3017,12 +3012,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3040,10 +3035,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811968</v>
+        <v>132811929</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,21 +3046,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3078,10 +3073,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521278</v>
+        <v>521300</v>
       </c>
       <c r="R21" t="n">
-        <v>7009051</v>
+        <v>7009023</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3116,6 +3111,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad tallved i tallskog.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811970</v>
+        <v>132811902</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521326</v>
+        <v>521234</v>
       </c>
       <c r="R22" t="n">
-        <v>7008987</v>
+        <v>7008999</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811957</v>
+        <v>132811924</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521417</v>
+        <v>521413</v>
       </c>
       <c r="R30" t="n">
-        <v>7008923</v>
+        <v>7008949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4268,26 +4268,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4305,57 +4285,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132811914</v>
+        <v>132811957</v>
       </c>
       <c r="B31" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521257</v>
+        <v>521417</v>
       </c>
       <c r="R31" t="n">
-        <v>7008967</v>
+        <v>7008923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4390,23 +4361,39 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4424,50 +4411,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811949</v>
+        <v>132811914</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4479,10 +4458,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521297</v>
+        <v>521257</v>
       </c>
       <c r="R32" t="n">
-        <v>7009058</v>
+        <v>7008967</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4519,7 +4498,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4528,13 +4507,12 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4552,10 +4530,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811924</v>
+        <v>132811988</v>
       </c>
       <c r="B33" t="n">
-        <v>80466</v>
+        <v>101338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4563,26 +4541,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4590,10 +4573,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521413</v>
+        <v>521434</v>
       </c>
       <c r="R33" t="n">
-        <v>7008949</v>
+        <v>7008976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4628,6 +4611,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4640,7 +4628,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4658,53 +4646,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811988</v>
+        <v>132811949</v>
       </c>
       <c r="B34" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521434</v>
+        <v>521297</v>
       </c>
       <c r="R34" t="n">
-        <v>7008976</v>
+        <v>7009058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132840100</v>
+        <v>132840092</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>91971</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521390</v>
+        <v>521309</v>
       </c>
       <c r="R52" t="n">
-        <v>7009025</v>
+        <v>7008998</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,6 +6699,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6715,10 +6730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132840092</v>
+        <v>132840100</v>
       </c>
       <c r="B53" t="n">
-        <v>91971</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6726,21 +6741,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6750,10 +6765,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521309</v>
+        <v>521390</v>
       </c>
       <c r="R53" t="n">
-        <v>7008998</v>
+        <v>7009025</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6785,7 +6800,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6795,7 +6810,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6806,21 +6821,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840099</v>
+        <v>132840126</v>
       </c>
       <c r="B58" t="n">
-        <v>92217</v>
+        <v>79923</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521388</v>
+        <v>521285</v>
       </c>
       <c r="R58" t="n">
-        <v>7009026</v>
+        <v>7008886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132840126</v>
+        <v>132840123</v>
       </c>
       <c r="B59" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7403,21 +7403,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521285</v>
+        <v>521310</v>
       </c>
       <c r="R59" t="n">
-        <v>7008886</v>
+        <v>7008918</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840123</v>
+        <v>132840099</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>92217</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521310</v>
+        <v>521388</v>
       </c>
       <c r="R60" t="n">
-        <v>7008918</v>
+        <v>7009026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7606,10 +7606,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132840098</v>
+        <v>132840096</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521390</v>
+        <v>521376</v>
       </c>
       <c r="R61" t="n">
-        <v>7009005</v>
+        <v>7009026</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7713,10 +7713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132840096</v>
+        <v>132840098</v>
       </c>
       <c r="B62" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7724,21 +7724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521376</v>
+        <v>521390</v>
       </c>
       <c r="R62" t="n">
-        <v>7009026</v>
+        <v>7009005</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -10584,10 +10584,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934508</v>
+        <v>132934661</v>
       </c>
       <c r="B91" t="n">
-        <v>91918</v>
+        <v>79090</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10595,34 +10595,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521332</v>
+        <v>521456</v>
       </c>
       <c r="R91" t="n">
-        <v>7009041</v>
+        <v>7008920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,32 +10681,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934711</v>
+        <v>132934705</v>
       </c>
       <c r="B92" t="n">
-        <v>92192</v>
+        <v>79333</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521269</v>
+        <v>521416</v>
       </c>
       <c r="R92" t="n">
-        <v>7008900</v>
+        <v>7008940</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10778,32 +10778,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934723</v>
+        <v>132934699</v>
       </c>
       <c r="B93" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521262</v>
+        <v>521371</v>
       </c>
       <c r="R93" t="n">
-        <v>7009041</v>
+        <v>7009040</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10843,12 +10843,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10875,45 +10875,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934668</v>
+        <v>132934508</v>
       </c>
       <c r="B94" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521460</v>
+        <v>521332</v>
       </c>
       <c r="R94" t="n">
-        <v>7008862</v>
+        <v>7009041</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10940,17 +10940,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10977,32 +10972,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934661</v>
+        <v>132934711</v>
       </c>
       <c r="B95" t="n">
-        <v>79090</v>
+        <v>92192</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521456</v>
+        <v>521269</v>
       </c>
       <c r="R95" t="n">
-        <v>7008920</v>
+        <v>7008900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11074,32 +11069,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934705</v>
+        <v>132934723</v>
       </c>
       <c r="B96" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11109,10 +11104,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521416</v>
+        <v>521262</v>
       </c>
       <c r="R96" t="n">
-        <v>7008940</v>
+        <v>7009041</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11171,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934699</v>
+        <v>132934668</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11206,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521371</v>
+        <v>521460</v>
       </c>
       <c r="R97" t="n">
-        <v>7009040</v>
+        <v>7008862</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11236,12 +11231,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B106" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R106" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,6 +12115,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12141,32 +12146,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B107" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12176,10 +12181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R107" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12212,11 +12217,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12539,32 +12539,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934645</v>
+        <v>132934651</v>
       </c>
       <c r="B111" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521343</v>
+        <v>521370</v>
       </c>
       <c r="R111" t="n">
-        <v>7009058</v>
+        <v>7009038</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12604,17 +12604,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12641,32 +12636,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934651</v>
+        <v>132934645</v>
       </c>
       <c r="B112" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12676,10 +12671,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521370</v>
+        <v>521343</v>
       </c>
       <c r="R112" t="n">
-        <v>7009038</v>
+        <v>7009058</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12706,12 +12701,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13708,10 +13708,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934622</v>
+        <v>132934731</v>
       </c>
       <c r="B123" t="n">
-        <v>79091</v>
+        <v>78340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521453</v>
+        <v>521235</v>
       </c>
       <c r="R123" t="n">
-        <v>7008881</v>
+        <v>7009006</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934731</v>
+        <v>132934720</v>
       </c>
       <c r="B124" t="n">
-        <v>78340</v>
+        <v>93206</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521235</v>
+        <v>521341</v>
       </c>
       <c r="R124" t="n">
-        <v>7009006</v>
+        <v>7008936</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934720</v>
+        <v>132934622</v>
       </c>
       <c r="B125" t="n">
-        <v>93206</v>
+        <v>79091</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521341</v>
+        <v>521453</v>
       </c>
       <c r="R125" t="n">
-        <v>7008936</v>
+        <v>7008881</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15357,32 +15357,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132934636</v>
+        <v>132934648</v>
       </c>
       <c r="B140" t="n">
-        <v>80438</v>
+        <v>80305</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>521362</v>
+        <v>521468</v>
       </c>
       <c r="R140" t="n">
-        <v>7009037</v>
+        <v>7008870</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15422,12 +15422,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15436,6 +15436,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15454,10 +15455,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132934537</v>
+        <v>132934509</v>
       </c>
       <c r="B141" t="n">
-        <v>79090</v>
+        <v>91918</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15465,21 +15466,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15489,10 +15490,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>521253</v>
+        <v>521329</v>
       </c>
       <c r="R141" t="n">
-        <v>7009010</v>
+        <v>7009049</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15551,32 +15552,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934648</v>
+        <v>132934561</v>
       </c>
       <c r="B142" t="n">
-        <v>80305</v>
+        <v>91840</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>385</v>
+        <v>3242</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15586,10 +15587,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521468</v>
+        <v>521263</v>
       </c>
       <c r="R142" t="n">
-        <v>7008870</v>
+        <v>7008978</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15630,7 +15631,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15649,10 +15649,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934509</v>
+        <v>132934636</v>
       </c>
       <c r="B143" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15660,34 +15660,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521329</v>
+        <v>521362</v>
       </c>
       <c r="R143" t="n">
-        <v>7009049</v>
+        <v>7009037</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15746,10 +15746,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934561</v>
+        <v>132934537</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>79090</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15757,34 +15757,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521263</v>
+        <v>521253</v>
       </c>
       <c r="R144" t="n">
-        <v>7008978</v>
+        <v>7009010</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15811,12 +15811,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R2" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,26 +764,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B3" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R3" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +857,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,6 +875,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2265,65 +2265,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132811943</v>
+        <v>132811972</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521374</v>
+        <v>521260</v>
       </c>
       <c r="R15" t="n">
-        <v>7008999</v>
+        <v>7008973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2360,7 +2343,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
+          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,7 +2358,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2393,48 +2396,65 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132811972</v>
+        <v>132811943</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521260</v>
+        <v>521374</v>
       </c>
       <c r="R16" t="n">
-        <v>7008973</v>
+        <v>7008999</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2471,7 +2491,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,27 +2506,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811968</v>
+        <v>132811929</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2794,21 +2794,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521278</v>
+        <v>521300</v>
       </c>
       <c r="R19" t="n">
-        <v>7009051</v>
+        <v>7009023</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2859,6 +2859,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad tallved i tallskog.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2886,12 +2891,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2909,10 +2914,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811970</v>
+        <v>132811902</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2920,21 +2925,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521326</v>
+        <v>521234</v>
       </c>
       <c r="R20" t="n">
-        <v>7008987</v>
+        <v>7008999</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2997,7 +3002,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3012,12 +3017,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3035,10 +3040,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811929</v>
+        <v>132811968</v>
       </c>
       <c r="B21" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3046,21 +3051,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3073,10 +3078,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521300</v>
+        <v>521278</v>
       </c>
       <c r="R21" t="n">
-        <v>7009023</v>
+        <v>7009051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3111,11 +3116,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På kolad tallved i tallskog.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811902</v>
+        <v>132811970</v>
       </c>
       <c r="B22" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521234</v>
+        <v>521326</v>
       </c>
       <c r="R22" t="n">
-        <v>7008999</v>
+        <v>7008987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811924</v>
+        <v>132811957</v>
       </c>
       <c r="B30" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521413</v>
+        <v>521417</v>
       </c>
       <c r="R30" t="n">
-        <v>7008949</v>
+        <v>7008923</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4268,6 +4268,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,48 +4305,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132811957</v>
+        <v>132811914</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>57145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521417</v>
+        <v>521257</v>
       </c>
       <c r="R31" t="n">
-        <v>7008923</v>
+        <v>7008967</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4361,39 +4390,23 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4411,42 +4424,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811914</v>
+        <v>132811949</v>
       </c>
       <c r="B32" t="n">
-        <v>57145</v>
+        <v>99130</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4458,10 +4479,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521257</v>
+        <v>521297</v>
       </c>
       <c r="R32" t="n">
-        <v>7008967</v>
+        <v>7009058</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4498,7 +4519,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4507,12 +4528,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4530,10 +4552,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811988</v>
+        <v>132811924</v>
       </c>
       <c r="B33" t="n">
-        <v>101338</v>
+        <v>80466</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4541,31 +4563,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>6461</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4573,10 +4590,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521434</v>
+        <v>521413</v>
       </c>
       <c r="R33" t="n">
-        <v>7008976</v>
+        <v>7008949</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4611,11 +4628,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4628,7 +4640,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4646,65 +4658,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811949</v>
+        <v>132811988</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>101338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521297</v>
+        <v>521434</v>
       </c>
       <c r="R34" t="n">
-        <v>7009058</v>
+        <v>7008976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840126</v>
+        <v>132840099</v>
       </c>
       <c r="B58" t="n">
-        <v>79923</v>
+        <v>92217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521285</v>
+        <v>521388</v>
       </c>
       <c r="R58" t="n">
-        <v>7008886</v>
+        <v>7009026</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132840123</v>
+        <v>132840126</v>
       </c>
       <c r="B59" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7403,21 +7403,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521310</v>
+        <v>521285</v>
       </c>
       <c r="R59" t="n">
-        <v>7008918</v>
+        <v>7008886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840099</v>
+        <v>132840123</v>
       </c>
       <c r="B60" t="n">
-        <v>92217</v>
+        <v>79091</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521388</v>
+        <v>521310</v>
       </c>
       <c r="R60" t="n">
-        <v>7009026</v>
+        <v>7008918</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -9323,45 +9323,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934650</v>
+        <v>132934553</v>
       </c>
       <c r="B78" t="n">
-        <v>80398</v>
+        <v>92092</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>1503</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521384</v>
+        <v>521348</v>
       </c>
       <c r="R78" t="n">
-        <v>7009026</v>
+        <v>7008988</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9420,45 +9420,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934553</v>
+        <v>132934696</v>
       </c>
       <c r="B79" t="n">
-        <v>92092</v>
+        <v>79333</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521348</v>
+        <v>521297</v>
       </c>
       <c r="R79" t="n">
-        <v>7008988</v>
+        <v>7009003</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9517,32 +9517,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934696</v>
+        <v>132934650</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521297</v>
+        <v>521384</v>
       </c>
       <c r="R80" t="n">
-        <v>7009003</v>
+        <v>7009026</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10584,10 +10584,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934661</v>
+        <v>132934508</v>
       </c>
       <c r="B91" t="n">
-        <v>79090</v>
+        <v>91918</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10595,34 +10595,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521456</v>
+        <v>521332</v>
       </c>
       <c r="R91" t="n">
-        <v>7008920</v>
+        <v>7009041</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,32 +10681,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934705</v>
+        <v>132934711</v>
       </c>
       <c r="B92" t="n">
-        <v>79333</v>
+        <v>92192</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521416</v>
+        <v>521269</v>
       </c>
       <c r="R92" t="n">
-        <v>7008940</v>
+        <v>7008900</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10778,32 +10778,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934699</v>
+        <v>132934723</v>
       </c>
       <c r="B93" t="n">
-        <v>79333</v>
+        <v>93206</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521371</v>
+        <v>521262</v>
       </c>
       <c r="R93" t="n">
-        <v>7009040</v>
+        <v>7009041</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10843,12 +10843,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10875,45 +10875,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934508</v>
+        <v>132934668</v>
       </c>
       <c r="B94" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521332</v>
+        <v>521460</v>
       </c>
       <c r="R94" t="n">
-        <v>7009041</v>
+        <v>7008862</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10940,12 +10940,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10972,32 +10977,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934711</v>
+        <v>132934661</v>
       </c>
       <c r="B95" t="n">
-        <v>92192</v>
+        <v>79090</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521269</v>
+        <v>521456</v>
       </c>
       <c r="R95" t="n">
-        <v>7008900</v>
+        <v>7008920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11069,32 +11074,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934723</v>
+        <v>132934705</v>
       </c>
       <c r="B96" t="n">
-        <v>93206</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11104,10 +11109,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521262</v>
+        <v>521416</v>
       </c>
       <c r="R96" t="n">
-        <v>7009041</v>
+        <v>7008940</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11166,32 +11171,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934668</v>
+        <v>132934699</v>
       </c>
       <c r="B97" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11206,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521460</v>
+        <v>521371</v>
       </c>
       <c r="R97" t="n">
-        <v>7008862</v>
+        <v>7009040</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11231,17 +11236,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B106" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R106" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,11 +12115,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12146,32 +12141,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B107" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12181,10 +12176,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R107" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12217,6 +12212,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14193,32 +14193,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934659</v>
+        <v>132934718</v>
       </c>
       <c r="B128" t="n">
-        <v>80398</v>
+        <v>78999</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521290</v>
+        <v>521260</v>
       </c>
       <c r="R128" t="n">
-        <v>7009063</v>
+        <v>7008980</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14258,12 +14258,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14290,10 +14290,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132934581</v>
+        <v>132934719</v>
       </c>
       <c r="B129" t="n">
-        <v>79923</v>
+        <v>78999</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14301,21 +14301,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14325,10 +14325,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>521230</v>
+        <v>521236</v>
       </c>
       <c r="R129" t="n">
-        <v>7009003</v>
+        <v>7009013</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,32 +14387,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132934718</v>
+        <v>132934687</v>
       </c>
       <c r="B130" t="n">
-        <v>78999</v>
+        <v>92092</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14422,10 +14422,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>521260</v>
+        <v>521353</v>
       </c>
       <c r="R130" t="n">
-        <v>7008980</v>
+        <v>7008975</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14452,12 +14452,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14484,32 +14484,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132934719</v>
+        <v>132934722</v>
       </c>
       <c r="B131" t="n">
-        <v>78999</v>
+        <v>93206</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>521236</v>
+        <v>521256</v>
       </c>
       <c r="R131" t="n">
-        <v>7009013</v>
+        <v>7009005</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14581,32 +14581,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132934687</v>
+        <v>132934659</v>
       </c>
       <c r="B132" t="n">
-        <v>92092</v>
+        <v>80398</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1503</v>
+        <v>229497</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14616,10 +14616,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>521353</v>
+        <v>521290</v>
       </c>
       <c r="R132" t="n">
-        <v>7008975</v>
+        <v>7009063</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14678,32 +14678,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132934722</v>
+        <v>132934581</v>
       </c>
       <c r="B133" t="n">
-        <v>93206</v>
+        <v>79923</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>521256</v>
+        <v>521230</v>
       </c>
       <c r="R133" t="n">
-        <v>7009005</v>
+        <v>7009003</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132811926</v>
+        <v>132811955</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521350</v>
+        <v>521458</v>
       </c>
       <c r="R2" t="n">
-        <v>7008993</v>
+        <v>7008895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på bark av tall i tallskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,32 +806,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132811955</v>
+        <v>132811926</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521458</v>
+        <v>521350</v>
       </c>
       <c r="R3" t="n">
-        <v>7008895</v>
+        <v>7008993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +882,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på bark av tall i tallskog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,26 +895,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1626,41 +1626,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132811932</v>
+        <v>132811916</v>
       </c>
       <c r="B10" t="n">
-        <v>80438</v>
+        <v>104642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521288</v>
+        <v>521428</v>
       </c>
       <c r="R10" t="n">
-        <v>7008966</v>
+        <v>7008979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,6 +1707,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1718,32 +1724,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En högstubbe.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula # En högstubbe.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1761,42 +1742,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132811916</v>
+        <v>132811932</v>
       </c>
       <c r="B11" t="n">
-        <v>104642</v>
+        <v>80438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1804,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521428</v>
+        <v>521288</v>
       </c>
       <c r="R11" t="n">
-        <v>7008979</v>
+        <v>7008966</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,11 +1822,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1859,7 +1834,32 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>En högstubbe.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula # En högstubbe.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2265,48 +2265,65 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132811972</v>
+        <v>132811943</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521260</v>
+        <v>521374</v>
       </c>
       <c r="R15" t="n">
-        <v>7008973</v>
+        <v>7008999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2343,7 +2360,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,27 +2375,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2396,65 +2393,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132811943</v>
+        <v>132811972</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521374</v>
+        <v>521260</v>
       </c>
       <c r="R16" t="n">
-        <v>7008999</v>
+        <v>7008973</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,7 +2471,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
+          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,7 +2486,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -4179,32 +4179,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132811957</v>
+        <v>132811924</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>80466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521417</v>
+        <v>521413</v>
       </c>
       <c r="R30" t="n">
-        <v>7008923</v>
+        <v>7008949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4268,26 +4268,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4305,57 +4285,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132811914</v>
+        <v>132811957</v>
       </c>
       <c r="B31" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521257</v>
+        <v>521417</v>
       </c>
       <c r="R31" t="n">
-        <v>7008967</v>
+        <v>7008923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4390,23 +4361,39 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4424,50 +4411,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132811949</v>
+        <v>132811914</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4479,10 +4458,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521297</v>
+        <v>521257</v>
       </c>
       <c r="R32" t="n">
-        <v>7009058</v>
+        <v>7008967</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4519,7 +4498,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
+          <t>Färsk spillning troligen av tupp i luftig blockrik tallskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4528,13 +4507,12 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4552,10 +4530,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132811924</v>
+        <v>132811988</v>
       </c>
       <c r="B33" t="n">
-        <v>80466</v>
+        <v>101338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4563,26 +4541,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4590,10 +4573,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521413</v>
+        <v>521434</v>
       </c>
       <c r="R33" t="n">
-        <v>7008949</v>
+        <v>7008976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4628,6 +4611,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Vid ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4640,7 +4628,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4658,53 +4646,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132811988</v>
+        <v>132811949</v>
       </c>
       <c r="B34" t="n">
-        <v>101338</v>
+        <v>99130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521434</v>
+        <v>521297</v>
       </c>
       <c r="R34" t="n">
-        <v>7008976</v>
+        <v>7009058</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Vid ett fuktstråk i barrblandskog.</t>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840099</v>
+        <v>132840126</v>
       </c>
       <c r="B58" t="n">
-        <v>92217</v>
+        <v>79923</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521388</v>
+        <v>521285</v>
       </c>
       <c r="R58" t="n">
-        <v>7009026</v>
+        <v>7008886</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132840126</v>
+        <v>132840123</v>
       </c>
       <c r="B59" t="n">
-        <v>79923</v>
+        <v>79091</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7403,21 +7403,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521285</v>
+        <v>521310</v>
       </c>
       <c r="R59" t="n">
-        <v>7008886</v>
+        <v>7008918</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840123</v>
+        <v>132840099</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>92217</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521310</v>
+        <v>521388</v>
       </c>
       <c r="R60" t="n">
-        <v>7008918</v>
+        <v>7009026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -9323,45 +9323,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132934553</v>
+        <v>132934650</v>
       </c>
       <c r="B78" t="n">
-        <v>92092</v>
+        <v>80398</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>521348</v>
+        <v>521384</v>
       </c>
       <c r="R78" t="n">
-        <v>7008988</v>
+        <v>7009026</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9420,45 +9420,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132934696</v>
+        <v>132934553</v>
       </c>
       <c r="B79" t="n">
-        <v>79333</v>
+        <v>92092</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>521297</v>
+        <v>521348</v>
       </c>
       <c r="R79" t="n">
-        <v>7009003</v>
+        <v>7008988</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9517,32 +9517,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132934650</v>
+        <v>132934696</v>
       </c>
       <c r="B80" t="n">
-        <v>80398</v>
+        <v>79333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>521384</v>
+        <v>521297</v>
       </c>
       <c r="R80" t="n">
-        <v>7009026</v>
+        <v>7009003</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11365,32 +11365,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934603</v>
+        <v>132934685</v>
       </c>
       <c r="B99" t="n">
-        <v>80342</v>
+        <v>92092</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521339</v>
+        <v>521278</v>
       </c>
       <c r="R99" t="n">
-        <v>7009060</v>
+        <v>7008985</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11462,10 +11462,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934621</v>
+        <v>132934505</v>
       </c>
       <c r="B100" t="n">
-        <v>79091</v>
+        <v>97370</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11473,34 +11473,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521284</v>
+        <v>521304</v>
       </c>
       <c r="R100" t="n">
-        <v>7008883</v>
+        <v>7009055</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11559,32 +11559,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934580</v>
+        <v>132934603</v>
       </c>
       <c r="B101" t="n">
-        <v>79923</v>
+        <v>80342</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11594,10 +11594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521256</v>
+        <v>521339</v>
       </c>
       <c r="R101" t="n">
-        <v>7008979</v>
+        <v>7009060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11656,7 +11656,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934520</v>
+        <v>132934621</v>
       </c>
       <c r="B102" t="n">
         <v>79091</v>
@@ -11687,14 +11687,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521367</v>
+        <v>521284</v>
       </c>
       <c r="R102" t="n">
-        <v>7008928</v>
+        <v>7008883</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11721,12 +11721,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11753,32 +11753,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934685</v>
+        <v>132934580</v>
       </c>
       <c r="B103" t="n">
-        <v>92092</v>
+        <v>79923</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521278</v>
+        <v>521256</v>
       </c>
       <c r="R103" t="n">
-        <v>7008985</v>
+        <v>7008979</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11850,10 +11850,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934505</v>
+        <v>132934520</v>
       </c>
       <c r="B104" t="n">
-        <v>97370</v>
+        <v>79091</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11861,21 +11861,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11885,10 +11885,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521304</v>
+        <v>521367</v>
       </c>
       <c r="R104" t="n">
-        <v>7009055</v>
+        <v>7008928</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B106" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R106" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,6 +12115,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12141,32 +12146,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B107" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12176,10 +12181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R107" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12212,11 +12217,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12539,32 +12539,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934651</v>
+        <v>132934645</v>
       </c>
       <c r="B111" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521370</v>
+        <v>521343</v>
       </c>
       <c r="R111" t="n">
-        <v>7009038</v>
+        <v>7009058</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12604,12 +12604,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12636,32 +12641,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934645</v>
+        <v>132934651</v>
       </c>
       <c r="B112" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12671,10 +12676,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521343</v>
+        <v>521370</v>
       </c>
       <c r="R112" t="n">
-        <v>7009058</v>
+        <v>7009038</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12701,17 +12706,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -1626,42 +1626,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132811916</v>
+        <v>132811932</v>
       </c>
       <c r="B10" t="n">
-        <v>104642</v>
+        <v>80438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1669,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521428</v>
+        <v>521288</v>
       </c>
       <c r="R10" t="n">
-        <v>7008979</v>
+        <v>7008966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,11 +1706,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer i ett fuktstråk i barrblandskog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1724,7 +1718,32 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>En högstubbe.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula # En högstubbe.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1742,41 +1761,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132811932</v>
+        <v>132811916</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>104642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,10 +1804,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521288</v>
+        <v>521428</v>
       </c>
       <c r="R11" t="n">
-        <v>7008966</v>
+        <v>7008979</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,6 +1842,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer i ett fuktstråk i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1834,32 +1859,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En högstubbe.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula # En högstubbe.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2265,65 +2265,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132811943</v>
+        <v>132811972</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521374</v>
+        <v>521260</v>
       </c>
       <c r="R15" t="n">
-        <v>7008999</v>
+        <v>7008973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2360,7 +2343,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
+          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,7 +2358,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2393,48 +2396,65 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132811972</v>
+        <v>132811943</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dusnäsberget sydöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521260</v>
+        <v>521374</v>
       </c>
       <c r="R16" t="n">
-        <v>7008973</v>
+        <v>7008999</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2471,7 +2491,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på tallbark, 59 cm lång bål.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i tallskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2486,27 +2506,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132811929</v>
+        <v>132811968</v>
       </c>
       <c r="B19" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2794,21 +2794,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521300</v>
+        <v>521278</v>
       </c>
       <c r="R19" t="n">
-        <v>7009023</v>
+        <v>7009051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2859,11 +2859,6 @@
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På kolad tallved i tallskog.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2891,12 +2886,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Fire killed tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2914,10 +2909,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132811902</v>
+        <v>132811970</v>
       </c>
       <c r="B20" t="n">
-        <v>79923</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,21 +2920,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2952,10 +2947,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521234</v>
+        <v>521326</v>
       </c>
       <c r="R20" t="n">
-        <v>7008999</v>
+        <v>7008987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3002,7 +2997,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Tallskog på blockmark</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3017,12 +3012,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stump # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3040,10 +3035,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132811968</v>
+        <v>132811929</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,21 +3046,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3078,10 +3073,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521278</v>
+        <v>521300</v>
       </c>
       <c r="R21" t="n">
-        <v>7009051</v>
+        <v>7009023</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3116,6 +3111,11 @@
           <t>2026-04-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På kolad tallved i tallskog.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Branddödat träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Fire killed tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132811970</v>
+        <v>132811902</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521326</v>
+        <v>521234</v>
       </c>
       <c r="R22" t="n">
-        <v>7008987</v>
+        <v>7008999</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog på blockmark</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stump # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132840092</v>
+        <v>132840100</v>
       </c>
       <c r="B52" t="n">
-        <v>91971</v>
+        <v>91918</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521309</v>
+        <v>521390</v>
       </c>
       <c r="R52" t="n">
-        <v>7008998</v>
+        <v>7009025</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,21 +6699,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6730,10 +6715,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132840100</v>
+        <v>132840092</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>91971</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6741,21 +6726,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6765,10 +6750,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521390</v>
+        <v>521309</v>
       </c>
       <c r="R53" t="n">
-        <v>7009025</v>
+        <v>7008998</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6800,7 +6785,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6810,7 +6795,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6821,6 +6806,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840126</v>
+        <v>132840099</v>
       </c>
       <c r="B58" t="n">
-        <v>79923</v>
+        <v>92217</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521285</v>
+        <v>521388</v>
       </c>
       <c r="R58" t="n">
-        <v>7008886</v>
+        <v>7009026</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132840123</v>
+        <v>132840126</v>
       </c>
       <c r="B59" t="n">
-        <v>79091</v>
+        <v>79923</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7403,21 +7403,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7427,10 +7427,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521310</v>
+        <v>521285</v>
       </c>
       <c r="R59" t="n">
-        <v>7008918</v>
+        <v>7008886</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840099</v>
+        <v>132840123</v>
       </c>
       <c r="B60" t="n">
-        <v>92217</v>
+        <v>79091</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521388</v>
+        <v>521310</v>
       </c>
       <c r="R60" t="n">
-        <v>7009026</v>
+        <v>7008918</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B106" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R106" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,11 +12115,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12146,32 +12141,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B107" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12181,10 +12176,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R107" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12217,6 +12212,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12539,32 +12539,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934645</v>
+        <v>132934651</v>
       </c>
       <c r="B111" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521343</v>
+        <v>521370</v>
       </c>
       <c r="R111" t="n">
-        <v>7009058</v>
+        <v>7009038</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12604,17 +12604,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12641,32 +12636,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934651</v>
+        <v>132934645</v>
       </c>
       <c r="B112" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12676,10 +12671,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521370</v>
+        <v>521343</v>
       </c>
       <c r="R112" t="n">
-        <v>7009038</v>
+        <v>7009058</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12706,12 +12701,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13708,10 +13708,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934731</v>
+        <v>132934622</v>
       </c>
       <c r="B123" t="n">
-        <v>78340</v>
+        <v>79091</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521235</v>
+        <v>521453</v>
       </c>
       <c r="R123" t="n">
-        <v>7009006</v>
+        <v>7008881</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934720</v>
+        <v>132934731</v>
       </c>
       <c r="B124" t="n">
-        <v>93206</v>
+        <v>78340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521341</v>
+        <v>521235</v>
       </c>
       <c r="R124" t="n">
-        <v>7008936</v>
+        <v>7009006</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934622</v>
+        <v>132934720</v>
       </c>
       <c r="B125" t="n">
-        <v>79091</v>
+        <v>93206</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521453</v>
+        <v>521341</v>
       </c>
       <c r="R125" t="n">
-        <v>7008881</v>
+        <v>7008936</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -4777,7 +4777,7 @@
         <v>132840097</v>
       </c>
       <c r="B35" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>132840089</v>
       </c>
       <c r="B36" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>132840112</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>132840125</v>
       </c>
       <c r="B38" t="n">
-        <v>92192</v>
+        <v>92194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>132840095</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>132840102</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132840108</v>
+        <v>132840103</v>
       </c>
       <c r="B41" t="n">
-        <v>91918</v>
+        <v>83316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5427,21 +5427,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521417</v>
+        <v>521403</v>
       </c>
       <c r="R41" t="n">
-        <v>7008986</v>
+        <v>7008996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,10 +5523,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132840111</v>
+        <v>132840108</v>
       </c>
       <c r="B42" t="n">
-        <v>78345</v>
+        <v>91920</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5534,21 +5534,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521478</v>
+        <v>521417</v>
       </c>
       <c r="R42" t="n">
-        <v>7008952</v>
+        <v>7008986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132840103</v>
+        <v>132840111</v>
       </c>
       <c r="B43" t="n">
-        <v>83315</v>
+        <v>78346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5641,21 +5641,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521403</v>
+        <v>521478</v>
       </c>
       <c r="R43" t="n">
-        <v>7008996</v>
+        <v>7008952</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5740,7 +5740,7 @@
         <v>132840120</v>
       </c>
       <c r="B44" t="n">
-        <v>80304</v>
+        <v>80305</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>132840110</v>
       </c>
       <c r="B45" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>132840106</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>132840116</v>
       </c>
       <c r="B47" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>132840124</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>132840091</v>
       </c>
       <c r="B49" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>132840113</v>
       </c>
       <c r="B50" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>132840088</v>
       </c>
       <c r="B51" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132840100</v>
+        <v>132840092</v>
       </c>
       <c r="B52" t="n">
-        <v>91918</v>
+        <v>91973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521390</v>
+        <v>521309</v>
       </c>
       <c r="R52" t="n">
-        <v>7009025</v>
+        <v>7008998</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6699,6 +6699,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6715,10 +6730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132840092</v>
+        <v>132840100</v>
       </c>
       <c r="B53" t="n">
-        <v>91971</v>
+        <v>91920</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6726,21 +6741,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6750,10 +6765,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521309</v>
+        <v>521390</v>
       </c>
       <c r="R53" t="n">
-        <v>7008998</v>
+        <v>7009025</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6785,7 +6800,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6795,7 +6810,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6806,21 +6821,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6840,7 +6840,7 @@
         <v>132840101</v>
       </c>
       <c r="B54" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>132840090</v>
       </c>
       <c r="B55" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>132840087</v>
       </c>
       <c r="B56" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>132840127</v>
       </c>
       <c r="B57" t="n">
-        <v>78736</v>
+        <v>78737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7285,10 +7285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132840099</v>
+        <v>132840123</v>
       </c>
       <c r="B58" t="n">
-        <v>92217</v>
+        <v>79092</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7296,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521388</v>
+        <v>521310</v>
       </c>
       <c r="R58" t="n">
-        <v>7009026</v>
+        <v>7008918</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7395,7 +7395,7 @@
         <v>132840126</v>
       </c>
       <c r="B59" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7499,10 +7499,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132840123</v>
+        <v>132840099</v>
       </c>
       <c r="B60" t="n">
-        <v>79091</v>
+        <v>92219</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7510,21 +7510,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7534,10 +7534,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521310</v>
+        <v>521388</v>
       </c>
       <c r="R60" t="n">
-        <v>7008918</v>
+        <v>7009026</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7606,10 +7606,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132840096</v>
+        <v>132840098</v>
       </c>
       <c r="B61" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521376</v>
+        <v>521390</v>
       </c>
       <c r="R61" t="n">
-        <v>7009026</v>
+        <v>7009005</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7713,10 +7713,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132840098</v>
+        <v>132840096</v>
       </c>
       <c r="B62" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7724,21 +7724,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521390</v>
+        <v>521376</v>
       </c>
       <c r="R62" t="n">
-        <v>7009005</v>
+        <v>7009026</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7823,7 +7823,7 @@
         <v>132840122</v>
       </c>
       <c r="B63" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>132934698</v>
       </c>
       <c r="B64" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>132934638</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8154,45 +8154,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934540</v>
+        <v>132934683</v>
       </c>
       <c r="B66" t="n">
-        <v>79090</v>
+        <v>92094</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521347</v>
+        <v>521412</v>
       </c>
       <c r="R66" t="n">
-        <v>7008990</v>
+        <v>7008950</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934556</v>
+        <v>132934540</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521357</v>
+        <v>521347</v>
       </c>
       <c r="R67" t="n">
-        <v>7008968</v>
+        <v>7008990</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,11 +8322,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8353,10 +8348,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934639</v>
+        <v>132934556</v>
       </c>
       <c r="B68" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8364,34 +8359,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521297</v>
+        <v>521357</v>
       </c>
       <c r="R68" t="n">
-        <v>7009054</v>
+        <v>7008968</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8424,6 +8419,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8450,32 +8450,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934683</v>
+        <v>132934639</v>
       </c>
       <c r="B69" t="n">
-        <v>92092</v>
+        <v>80439</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521412</v>
+        <v>521297</v>
       </c>
       <c r="R69" t="n">
-        <v>7008950</v>
+        <v>7009054</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8550,7 +8550,7 @@
         <v>132934632</v>
       </c>
       <c r="B70" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>132934654</v>
       </c>
       <c r="B71" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8741,32 +8741,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934635</v>
+        <v>132934656</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>80399</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521346</v>
+        <v>521300</v>
       </c>
       <c r="R72" t="n">
-        <v>7008992</v>
+        <v>7009071</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8838,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934538</v>
+        <v>132934635</v>
       </c>
       <c r="B73" t="n">
-        <v>79090</v>
+        <v>80439</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8849,34 +8849,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521314</v>
+        <v>521346</v>
       </c>
       <c r="R73" t="n">
-        <v>7008997</v>
+        <v>7008992</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8938,7 +8938,7 @@
         <v>132934708</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934617</v>
+        <v>132934538</v>
       </c>
       <c r="B75" t="n">
-        <v>91971</v>
+        <v>79091</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9043,34 +9043,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521420</v>
+        <v>521314</v>
       </c>
       <c r="R75" t="n">
-        <v>7008863</v>
+        <v>7008997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934713</v>
+        <v>132934617</v>
       </c>
       <c r="B76" t="n">
-        <v>92192</v>
+        <v>91973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521238</v>
+        <v>521420</v>
       </c>
       <c r="R76" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9226,32 +9226,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132934656</v>
+        <v>132934713</v>
       </c>
       <c r="B77" t="n">
-        <v>80398</v>
+        <v>92194</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>65</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9261,10 +9261,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521300</v>
+        <v>521238</v>
       </c>
       <c r="R77" t="n">
-        <v>7009071</v>
+        <v>7008997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9291,12 +9291,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9326,7 +9326,7 @@
         <v>132934650</v>
       </c>
       <c r="B78" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>132934553</v>
       </c>
       <c r="B79" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>132934696</v>
       </c>
       <c r="B80" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>132934706</v>
       </c>
       <c r="B81" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9711,32 +9711,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934707</v>
+        <v>132934688</v>
       </c>
       <c r="B82" t="n">
-        <v>79333</v>
+        <v>92094</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521289</v>
+        <v>521335</v>
       </c>
       <c r="R82" t="n">
-        <v>7008957</v>
+        <v>7009020</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9776,12 +9776,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934688</v>
+        <v>132934707</v>
       </c>
       <c r="B83" t="n">
-        <v>92092</v>
+        <v>79334</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521335</v>
+        <v>521289</v>
       </c>
       <c r="R83" t="n">
-        <v>7009020</v>
+        <v>7008957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9873,12 +9873,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934563</v>
+        <v>132934721</v>
       </c>
       <c r="B84" t="n">
-        <v>97370</v>
+        <v>93208</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521415</v>
+        <v>521464</v>
       </c>
       <c r="R84" t="n">
-        <v>7008980</v>
+        <v>7008859</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,32 +10002,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934721</v>
+        <v>132934563</v>
       </c>
       <c r="B85" t="n">
-        <v>93206</v>
+        <v>97372</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521464</v>
+        <v>521415</v>
       </c>
       <c r="R85" t="n">
-        <v>7008859</v>
+        <v>7008980</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10102,7 +10102,7 @@
         <v>132934624</v>
       </c>
       <c r="B86" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>132934623</v>
       </c>
       <c r="B87" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>132934700</v>
       </c>
       <c r="B88" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>132934692</v>
       </c>
       <c r="B89" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>132934682</v>
       </c>
       <c r="B90" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>132934508</v>
       </c>
       <c r="B91" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>132934711</v>
       </c>
       <c r="B92" t="n">
-        <v>92192</v>
+        <v>92194</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10778,32 +10778,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934723</v>
+        <v>132934668</v>
       </c>
       <c r="B93" t="n">
-        <v>93206</v>
+        <v>99132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521262</v>
+        <v>521460</v>
       </c>
       <c r="R93" t="n">
-        <v>7009041</v>
+        <v>7008862</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10849,6 +10849,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10875,32 +10880,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934668</v>
+        <v>132934657</v>
       </c>
       <c r="B94" t="n">
-        <v>99130</v>
+        <v>80399</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10910,10 +10915,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521460</v>
+        <v>521311</v>
       </c>
       <c r="R94" t="n">
-        <v>7008862</v>
+        <v>7009049</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10940,17 +10945,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10980,7 +10980,7 @@
         <v>132934661</v>
       </c>
       <c r="B95" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>132934705</v>
       </c>
       <c r="B96" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>132934699</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11268,10 +11268,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934657</v>
+        <v>132934723</v>
       </c>
       <c r="B98" t="n">
-        <v>80398</v>
+        <v>93208</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11279,21 +11279,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521311</v>
+        <v>521262</v>
       </c>
       <c r="R98" t="n">
-        <v>7009049</v>
+        <v>7009041</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11333,12 +11333,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11368,7 +11368,7 @@
         <v>132934685</v>
       </c>
       <c r="B99" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11462,45 +11462,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934505</v>
+        <v>132934603</v>
       </c>
       <c r="B100" t="n">
-        <v>97370</v>
+        <v>80343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521304</v>
+        <v>521339</v>
       </c>
       <c r="R100" t="n">
-        <v>7009055</v>
+        <v>7009060</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11559,45 +11559,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934603</v>
+        <v>132934505</v>
       </c>
       <c r="B101" t="n">
-        <v>80342</v>
+        <v>97372</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521339</v>
+        <v>521304</v>
       </c>
       <c r="R101" t="n">
-        <v>7009060</v>
+        <v>7009055</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11659,7 +11659,7 @@
         <v>132934621</v>
       </c>
       <c r="B102" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>132934580</v>
       </c>
       <c r="B103" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>132934520</v>
       </c>
       <c r="B104" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>132934643</v>
       </c>
       <c r="B105" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12044,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934649</v>
+        <v>132934669</v>
       </c>
       <c r="B106" t="n">
-        <v>80398</v>
+        <v>99132</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521472</v>
+        <v>521481</v>
       </c>
       <c r="R106" t="n">
-        <v>7008923</v>
+        <v>7008912</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,6 +12115,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12141,32 +12146,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132934669</v>
+        <v>132934649</v>
       </c>
       <c r="B107" t="n">
-        <v>99130</v>
+        <v>80399</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12176,10 +12181,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>521481</v>
+        <v>521472</v>
       </c>
       <c r="R107" t="n">
-        <v>7008912</v>
+        <v>7008923</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12212,11 +12217,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12246,7 +12246,7 @@
         <v>132934715</v>
       </c>
       <c r="B108" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12340,32 +12340,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934712</v>
+        <v>132934637</v>
       </c>
       <c r="B109" t="n">
-        <v>92192</v>
+        <v>80439</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>65</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12375,10 +12375,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521471</v>
+        <v>521330</v>
       </c>
       <c r="R109" t="n">
-        <v>7008872</v>
+        <v>7009056</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12405,12 +12405,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12437,32 +12442,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132934637</v>
+        <v>132934712</v>
       </c>
       <c r="B110" t="n">
-        <v>80438</v>
+        <v>92194</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12472,10 +12477,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>521330</v>
+        <v>521471</v>
       </c>
       <c r="R110" t="n">
-        <v>7009056</v>
+        <v>7008872</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12502,17 +12507,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12539,32 +12539,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132934651</v>
+        <v>132934645</v>
       </c>
       <c r="B111" t="n">
-        <v>80398</v>
+        <v>80439</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>521370</v>
+        <v>521343</v>
       </c>
       <c r="R111" t="n">
-        <v>7009038</v>
+        <v>7009058</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12604,12 +12604,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12636,32 +12641,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132934645</v>
+        <v>132934651</v>
       </c>
       <c r="B112" t="n">
-        <v>80438</v>
+        <v>80399</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12671,10 +12676,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>521343</v>
+        <v>521370</v>
       </c>
       <c r="R112" t="n">
-        <v>7009058</v>
+        <v>7009038</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12701,17 +12706,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12738,32 +12738,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934717</v>
+        <v>132934689</v>
       </c>
       <c r="B113" t="n">
-        <v>78999</v>
+        <v>92094</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521268</v>
+        <v>521289</v>
       </c>
       <c r="R113" t="n">
-        <v>7008957</v>
+        <v>7009060</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12803,12 +12803,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12835,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934584</v>
+        <v>132934732</v>
       </c>
       <c r="B114" t="n">
-        <v>91918</v>
+        <v>78737</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12846,21 +12846,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521471</v>
+        <v>521236</v>
       </c>
       <c r="R114" t="n">
-        <v>7008946</v>
+        <v>7009004</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12932,32 +12932,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934689</v>
+        <v>132934717</v>
       </c>
       <c r="B115" t="n">
-        <v>92092</v>
+        <v>79000</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521289</v>
+        <v>521268</v>
       </c>
       <c r="R115" t="n">
-        <v>7009060</v>
+        <v>7008957</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12997,12 +12997,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13029,10 +13029,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934518</v>
+        <v>132934584</v>
       </c>
       <c r="B116" t="n">
-        <v>79091</v>
+        <v>91920</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13040,34 +13040,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521253</v>
+        <v>521471</v>
       </c>
       <c r="R116" t="n">
-        <v>7009010</v>
+        <v>7008946</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13094,12 +13094,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13126,10 +13126,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132934732</v>
+        <v>132934518</v>
       </c>
       <c r="B117" t="n">
-        <v>78736</v>
+        <v>79092</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13137,34 +13137,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>521236</v>
+        <v>521253</v>
       </c>
       <c r="R117" t="n">
-        <v>7009004</v>
+        <v>7009010</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13191,12 +13191,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13226,7 +13226,7 @@
         <v>132934539</v>
       </c>
       <c r="B118" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>132934697</v>
       </c>
       <c r="B119" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>132934658</v>
       </c>
       <c r="B120" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>132934695</v>
       </c>
       <c r="B121" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>132934644</v>
       </c>
       <c r="B122" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>132934622</v>
       </c>
       <c r="B123" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934731</v>
+        <v>132934720</v>
       </c>
       <c r="B124" t="n">
-        <v>78340</v>
+        <v>93208</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521235</v>
+        <v>521341</v>
       </c>
       <c r="R124" t="n">
-        <v>7009006</v>
+        <v>7008936</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934720</v>
+        <v>132934731</v>
       </c>
       <c r="B125" t="n">
-        <v>93206</v>
+        <v>78341</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521341</v>
+        <v>521235</v>
       </c>
       <c r="R125" t="n">
-        <v>7008936</v>
+        <v>7009006</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14002,7 +14002,7 @@
         <v>132934512</v>
       </c>
       <c r="B126" t="n">
-        <v>80304</v>
+        <v>80305</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>132934716</v>
       </c>
       <c r="B127" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14193,32 +14193,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934718</v>
+        <v>132934687</v>
       </c>
       <c r="B128" t="n">
-        <v>78999</v>
+        <v>92094</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521260</v>
+        <v>521353</v>
       </c>
       <c r="R128" t="n">
-        <v>7008980</v>
+        <v>7008975</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14258,12 +14258,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14290,32 +14290,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132934719</v>
+        <v>132934722</v>
       </c>
       <c r="B129" t="n">
-        <v>78999</v>
+        <v>93208</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14325,10 +14325,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>521236</v>
+        <v>521256</v>
       </c>
       <c r="R129" t="n">
-        <v>7009013</v>
+        <v>7009005</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14387,32 +14387,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132934687</v>
+        <v>132934718</v>
       </c>
       <c r="B130" t="n">
-        <v>92092</v>
+        <v>79000</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14422,10 +14422,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>521353</v>
+        <v>521260</v>
       </c>
       <c r="R130" t="n">
-        <v>7008975</v>
+        <v>7008980</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14452,12 +14452,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14484,32 +14484,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132934722</v>
+        <v>132934719</v>
       </c>
       <c r="B131" t="n">
-        <v>93206</v>
+        <v>79000</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>521256</v>
+        <v>521236</v>
       </c>
       <c r="R131" t="n">
-        <v>7009005</v>
+        <v>7009013</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14584,7 +14584,7 @@
         <v>132934659</v>
       </c>
       <c r="B132" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>132934581</v>
       </c>
       <c r="B133" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132934568</v>
+        <v>132934714</v>
       </c>
       <c r="B134" t="n">
-        <v>79952</v>
+        <v>79000</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>521278</v>
+        <v>521381</v>
       </c>
       <c r="R134" t="n">
-        <v>7008986</v>
+        <v>7008904</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132934694</v>
+        <v>132934519</v>
       </c>
       <c r="B135" t="n">
-        <v>79333</v>
+        <v>79092</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14883,34 +14883,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>521463</v>
+        <v>521418</v>
       </c>
       <c r="R135" t="n">
-        <v>7008881</v>
+        <v>7008891</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14937,12 +14937,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14969,10 +14969,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132934714</v>
+        <v>132934579</v>
       </c>
       <c r="B136" t="n">
-        <v>78999</v>
+        <v>79924</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14980,21 +14980,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15004,10 +15004,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>521381</v>
+        <v>521343</v>
       </c>
       <c r="R136" t="n">
-        <v>7008904</v>
+        <v>7008898</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15066,32 +15066,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132934686</v>
+        <v>132934568</v>
       </c>
       <c r="B137" t="n">
-        <v>92092</v>
+        <v>79953</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>521364</v>
+        <v>521278</v>
       </c>
       <c r="R137" t="n">
-        <v>7008948</v>
+        <v>7008986</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15163,10 +15163,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132934519</v>
+        <v>132934694</v>
       </c>
       <c r="B138" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15174,34 +15174,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>521418</v>
+        <v>521463</v>
       </c>
       <c r="R138" t="n">
-        <v>7008891</v>
+        <v>7008881</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15228,12 +15228,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15260,32 +15260,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132934579</v>
+        <v>132934686</v>
       </c>
       <c r="B139" t="n">
-        <v>79923</v>
+        <v>92094</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>521343</v>
+        <v>521364</v>
       </c>
       <c r="R139" t="n">
-        <v>7008898</v>
+        <v>7008948</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15325,12 +15325,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15357,32 +15357,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132934648</v>
+        <v>132934636</v>
       </c>
       <c r="B140" t="n">
-        <v>80305</v>
+        <v>80439</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15392,10 +15392,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>521468</v>
+        <v>521362</v>
       </c>
       <c r="R140" t="n">
-        <v>7008870</v>
+        <v>7009037</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15422,12 +15422,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15436,7 +15436,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15455,10 +15454,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132934509</v>
+        <v>132934537</v>
       </c>
       <c r="B141" t="n">
-        <v>91918</v>
+        <v>79091</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15466,21 +15465,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15490,10 +15489,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>521329</v>
+        <v>521253</v>
       </c>
       <c r="R141" t="n">
-        <v>7009049</v>
+        <v>7009010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15555,7 +15554,7 @@
         <v>132934561</v>
       </c>
       <c r="B142" t="n">
-        <v>91840</v>
+        <v>91842</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15649,32 +15648,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934636</v>
+        <v>132934648</v>
       </c>
       <c r="B143" t="n">
-        <v>80438</v>
+        <v>80306</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15684,10 +15683,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521362</v>
+        <v>521468</v>
       </c>
       <c r="R143" t="n">
-        <v>7009037</v>
+        <v>7008870</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15714,12 +15713,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15728,6 +15727,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15746,10 +15746,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934537</v>
+        <v>132934509</v>
       </c>
       <c r="B144" t="n">
-        <v>79090</v>
+        <v>91920</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15757,21 +15757,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15781,10 +15781,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521253</v>
+        <v>521329</v>
       </c>
       <c r="R144" t="n">
-        <v>7009010</v>
+        <v>7009049</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15846,7 +15846,7 @@
         <v>132934652</v>
       </c>
       <c r="B145" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>132934578</v>
       </c>
       <c r="B146" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>132934653</v>
       </c>
       <c r="B147" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>132934536</v>
       </c>
       <c r="B148" t="n">
-        <v>80398</v>
+        <v>80399</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -8741,32 +8741,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132934656</v>
+        <v>132934635</v>
       </c>
       <c r="B72" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8776,10 +8776,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521300</v>
+        <v>521346</v>
       </c>
       <c r="R72" t="n">
-        <v>7009071</v>
+        <v>7008992</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8838,10 +8838,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934635</v>
+        <v>132934708</v>
       </c>
       <c r="B73" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8849,21 +8849,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521346</v>
+        <v>521276</v>
       </c>
       <c r="R73" t="n">
-        <v>7008992</v>
+        <v>7009057</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934708</v>
+        <v>132934538</v>
       </c>
       <c r="B74" t="n">
-        <v>79334</v>
+        <v>79091</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8946,34 +8946,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521276</v>
+        <v>521314</v>
       </c>
       <c r="R74" t="n">
-        <v>7009057</v>
+        <v>7008997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9032,10 +9032,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934538</v>
+        <v>132934617</v>
       </c>
       <c r="B75" t="n">
-        <v>79091</v>
+        <v>91973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9043,34 +9043,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521314</v>
+        <v>521420</v>
       </c>
       <c r="R75" t="n">
-        <v>7008997</v>
+        <v>7008863</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934617</v>
+        <v>132934656</v>
       </c>
       <c r="B76" t="n">
-        <v>91973</v>
+        <v>80399</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2079</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521420</v>
+        <v>521300</v>
       </c>
       <c r="R76" t="n">
-        <v>7008863</v>
+        <v>7009071</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10584,10 +10584,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132934508</v>
+        <v>132934661</v>
       </c>
       <c r="B91" t="n">
-        <v>91920</v>
+        <v>79091</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10595,34 +10595,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>521332</v>
+        <v>521456</v>
       </c>
       <c r="R91" t="n">
-        <v>7009041</v>
+        <v>7008920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10681,32 +10681,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934711</v>
+        <v>132934705</v>
       </c>
       <c r="B92" t="n">
-        <v>92194</v>
+        <v>79334</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521269</v>
+        <v>521416</v>
       </c>
       <c r="R92" t="n">
-        <v>7008900</v>
+        <v>7008940</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10778,32 +10778,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934668</v>
+        <v>132934699</v>
       </c>
       <c r="B93" t="n">
-        <v>99132</v>
+        <v>79334</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521460</v>
+        <v>521371</v>
       </c>
       <c r="R93" t="n">
-        <v>7008862</v>
+        <v>7009040</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10843,17 +10843,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10880,10 +10875,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934657</v>
+        <v>132934723</v>
       </c>
       <c r="B94" t="n">
-        <v>80399</v>
+        <v>93208</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10891,21 +10886,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229497</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10915,10 +10910,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521311</v>
+        <v>521262</v>
       </c>
       <c r="R94" t="n">
-        <v>7009049</v>
+        <v>7009041</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10945,12 +10940,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10977,32 +10972,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934661</v>
+        <v>132934657</v>
       </c>
       <c r="B95" t="n">
-        <v>79091</v>
+        <v>80399</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521456</v>
+        <v>521311</v>
       </c>
       <c r="R95" t="n">
-        <v>7008920</v>
+        <v>7009049</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11042,12 +11037,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11074,10 +11069,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934705</v>
+        <v>132934508</v>
       </c>
       <c r="B96" t="n">
-        <v>79334</v>
+        <v>91920</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11085,34 +11080,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521416</v>
+        <v>521332</v>
       </c>
       <c r="R96" t="n">
-        <v>7008940</v>
+        <v>7009041</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11139,12 +11134,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11171,32 +11166,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934699</v>
+        <v>132934711</v>
       </c>
       <c r="B97" t="n">
-        <v>79334</v>
+        <v>92194</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11206,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521371</v>
+        <v>521269</v>
       </c>
       <c r="R97" t="n">
-        <v>7009040</v>
+        <v>7008900</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11236,12 +11231,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11268,32 +11263,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934723</v>
+        <v>132934668</v>
       </c>
       <c r="B98" t="n">
-        <v>93208</v>
+        <v>99132</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11303,10 +11298,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521262</v>
+        <v>521460</v>
       </c>
       <c r="R98" t="n">
-        <v>7009041</v>
+        <v>7008862</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11339,6 +11334,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11947,32 +11947,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934643</v>
+        <v>132934669</v>
       </c>
       <c r="B105" t="n">
-        <v>80439</v>
+        <v>99132</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521368</v>
+        <v>521481</v>
       </c>
       <c r="R105" t="n">
-        <v>7009037</v>
+        <v>7008912</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,6 +12018,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12044,32 +12049,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934669</v>
+        <v>132934643</v>
       </c>
       <c r="B106" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12079,10 +12084,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521481</v>
+        <v>521368</v>
       </c>
       <c r="R106" t="n">
-        <v>7008912</v>
+        <v>7009037</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12115,11 +12120,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13708,32 +13708,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934622</v>
+        <v>132934720</v>
       </c>
       <c r="B123" t="n">
-        <v>79092</v>
+        <v>93208</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521453</v>
+        <v>521341</v>
       </c>
       <c r="R123" t="n">
-        <v>7008881</v>
+        <v>7008936</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934720</v>
+        <v>132934731</v>
       </c>
       <c r="B124" t="n">
-        <v>93208</v>
+        <v>78341</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521341</v>
+        <v>521235</v>
       </c>
       <c r="R124" t="n">
-        <v>7008936</v>
+        <v>7009006</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934731</v>
+        <v>132934622</v>
       </c>
       <c r="B125" t="n">
-        <v>78341</v>
+        <v>79092</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521235</v>
+        <v>521453</v>
       </c>
       <c r="R125" t="n">
-        <v>7009006</v>
+        <v>7008881</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14775,10 +14775,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132934714</v>
+        <v>132934568</v>
       </c>
       <c r="B134" t="n">
-        <v>79000</v>
+        <v>79953</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14786,21 +14786,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14810,10 +14810,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>521381</v>
+        <v>521278</v>
       </c>
       <c r="R134" t="n">
-        <v>7008904</v>
+        <v>7008986</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14872,10 +14872,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132934519</v>
+        <v>132934694</v>
       </c>
       <c r="B135" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14883,34 +14883,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>521418</v>
+        <v>521463</v>
       </c>
       <c r="R135" t="n">
-        <v>7008891</v>
+        <v>7008881</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14937,12 +14937,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14969,32 +14969,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132934579</v>
+        <v>132934686</v>
       </c>
       <c r="B136" t="n">
-        <v>79924</v>
+        <v>92094</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15004,10 +15004,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>521343</v>
+        <v>521364</v>
       </c>
       <c r="R136" t="n">
-        <v>7008898</v>
+        <v>7008948</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15066,10 +15066,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132934568</v>
+        <v>132934714</v>
       </c>
       <c r="B137" t="n">
-        <v>79953</v>
+        <v>79000</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15077,21 +15077,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>521278</v>
+        <v>521381</v>
       </c>
       <c r="R137" t="n">
-        <v>7008986</v>
+        <v>7008904</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15163,10 +15163,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132934694</v>
+        <v>132934519</v>
       </c>
       <c r="B138" t="n">
-        <v>79334</v>
+        <v>79092</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15174,34 +15174,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>521463</v>
+        <v>521418</v>
       </c>
       <c r="R138" t="n">
-        <v>7008881</v>
+        <v>7008891</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15228,12 +15228,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15260,32 +15260,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132934686</v>
+        <v>132934579</v>
       </c>
       <c r="B139" t="n">
-        <v>92094</v>
+        <v>79924</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15295,10 +15295,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>521364</v>
+        <v>521343</v>
       </c>
       <c r="R139" t="n">
-        <v>7008948</v>
+        <v>7008898</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15325,12 +15325,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD139" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -10002,10 +10002,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934563</v>
+        <v>132934624</v>
       </c>
       <c r="B85" t="n">
-        <v>97372</v>
+        <v>79092</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10013,21 +10013,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521415</v>
+        <v>521279</v>
       </c>
       <c r="R85" t="n">
-        <v>7008980</v>
+        <v>7008952</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10099,7 +10099,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934624</v>
+        <v>132934623</v>
       </c>
       <c r="B86" t="n">
         <v>79092</v>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521279</v>
+        <v>521457</v>
       </c>
       <c r="R86" t="n">
-        <v>7008952</v>
+        <v>7008866</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934623</v>
+        <v>132934563</v>
       </c>
       <c r="B87" t="n">
-        <v>79092</v>
+        <v>97372</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10207,21 +10207,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521457</v>
+        <v>521415</v>
       </c>
       <c r="R87" t="n">
-        <v>7008866</v>
+        <v>7008980</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -13708,32 +13708,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934720</v>
+        <v>132934622</v>
       </c>
       <c r="B123" t="n">
-        <v>93208</v>
+        <v>79092</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521341</v>
+        <v>521453</v>
       </c>
       <c r="R123" t="n">
-        <v>7008936</v>
+        <v>7008881</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934731</v>
+        <v>132934720</v>
       </c>
       <c r="B124" t="n">
-        <v>78341</v>
+        <v>93208</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521235</v>
+        <v>521341</v>
       </c>
       <c r="R124" t="n">
-        <v>7009006</v>
+        <v>7008936</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,10 +13902,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934622</v>
+        <v>132934731</v>
       </c>
       <c r="B125" t="n">
-        <v>79092</v>
+        <v>78341</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13913,21 +13913,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521453</v>
+        <v>521235</v>
       </c>
       <c r="R125" t="n">
-        <v>7008881</v>
+        <v>7009006</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -8154,45 +8154,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132934683</v>
+        <v>132934540</v>
       </c>
       <c r="B66" t="n">
-        <v>92094</v>
+        <v>79091</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521412</v>
+        <v>521347</v>
       </c>
       <c r="R66" t="n">
-        <v>7008950</v>
+        <v>7008990</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8251,10 +8251,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132934540</v>
+        <v>132934556</v>
       </c>
       <c r="B67" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521347</v>
+        <v>521357</v>
       </c>
       <c r="R67" t="n">
-        <v>7008990</v>
+        <v>7008968</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,6 +8322,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8348,10 +8353,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132934556</v>
+        <v>132934639</v>
       </c>
       <c r="B68" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8359,34 +8364,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521357</v>
+        <v>521297</v>
       </c>
       <c r="R68" t="n">
-        <v>7008968</v>
+        <v>7009054</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8419,11 +8424,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>60 cm lång, på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8450,32 +8450,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132934639</v>
+        <v>132934683</v>
       </c>
       <c r="B69" t="n">
-        <v>80439</v>
+        <v>92102</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8485,10 +8485,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521297</v>
+        <v>521412</v>
       </c>
       <c r="R69" t="n">
-        <v>7009054</v>
+        <v>7008950</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8838,32 +8838,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132934708</v>
+        <v>132934656</v>
       </c>
       <c r="B73" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521276</v>
+        <v>521300</v>
       </c>
       <c r="R73" t="n">
-        <v>7009057</v>
+        <v>7009071</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8935,10 +8935,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132934538</v>
+        <v>132934708</v>
       </c>
       <c r="B74" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8946,34 +8946,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521314</v>
+        <v>521276</v>
       </c>
       <c r="R74" t="n">
-        <v>7008997</v>
+        <v>7009057</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9032,10 +9032,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132934617</v>
+        <v>132934538</v>
       </c>
       <c r="B75" t="n">
-        <v>91973</v>
+        <v>79091</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9043,34 +9043,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521420</v>
+        <v>521314</v>
       </c>
       <c r="R75" t="n">
-        <v>7008863</v>
+        <v>7008997</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9097,12 +9097,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9129,32 +9129,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132934656</v>
+        <v>132934617</v>
       </c>
       <c r="B76" t="n">
-        <v>80399</v>
+        <v>91981</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>2079</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9164,10 +9164,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521300</v>
+        <v>521420</v>
       </c>
       <c r="R76" t="n">
-        <v>7009071</v>
+        <v>7008863</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9194,12 +9194,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9229,7 +9229,7 @@
         <v>132934713</v>
       </c>
       <c r="B77" t="n">
-        <v>92194</v>
+        <v>92202</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>132934553</v>
       </c>
       <c r="B79" t="n">
-        <v>92094</v>
+        <v>92102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9614,32 +9614,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132934706</v>
+        <v>132934688</v>
       </c>
       <c r="B81" t="n">
-        <v>79334</v>
+        <v>92102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>521426</v>
+        <v>521335</v>
       </c>
       <c r="R81" t="n">
-        <v>7008976</v>
+        <v>7009020</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9679,12 +9679,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9711,32 +9711,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132934688</v>
+        <v>132934563</v>
       </c>
       <c r="B82" t="n">
-        <v>92094</v>
+        <v>97380</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9746,10 +9746,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>521335</v>
+        <v>521415</v>
       </c>
       <c r="R82" t="n">
-        <v>7009020</v>
+        <v>7008980</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9776,12 +9776,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9808,32 +9808,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132934707</v>
+        <v>132934721</v>
       </c>
       <c r="B83" t="n">
-        <v>79334</v>
+        <v>93216</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9843,10 +9843,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>521289</v>
+        <v>521464</v>
       </c>
       <c r="R83" t="n">
-        <v>7008957</v>
+        <v>7008859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9905,32 +9905,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132934721</v>
+        <v>132934706</v>
       </c>
       <c r="B84" t="n">
-        <v>93208</v>
+        <v>79334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9940,10 +9940,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>521464</v>
+        <v>521426</v>
       </c>
       <c r="R84" t="n">
-        <v>7008859</v>
+        <v>7008976</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10002,10 +10002,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132934624</v>
+        <v>132934707</v>
       </c>
       <c r="B85" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10013,21 +10013,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>521279</v>
+        <v>521289</v>
       </c>
       <c r="R85" t="n">
-        <v>7008952</v>
+        <v>7008957</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10099,7 +10099,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132934623</v>
+        <v>132934624</v>
       </c>
       <c r="B86" t="n">
         <v>79092</v>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>521457</v>
+        <v>521279</v>
       </c>
       <c r="R86" t="n">
-        <v>7008866</v>
+        <v>7008952</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132934563</v>
+        <v>132934623</v>
       </c>
       <c r="B87" t="n">
-        <v>97372</v>
+        <v>79092</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10207,21 +10207,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10231,10 +10231,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>521415</v>
+        <v>521457</v>
       </c>
       <c r="R87" t="n">
-        <v>7008980</v>
+        <v>7008866</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10490,7 +10490,7 @@
         <v>132934682</v>
       </c>
       <c r="B90" t="n">
-        <v>92094</v>
+        <v>92102</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132934705</v>
+        <v>132934699</v>
       </c>
       <c r="B92" t="n">
         <v>79334</v>
@@ -10716,10 +10716,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>521416</v>
+        <v>521371</v>
       </c>
       <c r="R92" t="n">
-        <v>7008940</v>
+        <v>7009040</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10746,12 +10746,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10778,10 +10778,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132934699</v>
+        <v>132934508</v>
       </c>
       <c r="B93" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10789,34 +10789,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>521371</v>
+        <v>521332</v>
       </c>
       <c r="R93" t="n">
-        <v>7009040</v>
+        <v>7009041</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132934723</v>
+        <v>132934705</v>
       </c>
       <c r="B94" t="n">
-        <v>93208</v>
+        <v>79334</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>521262</v>
+        <v>521416</v>
       </c>
       <c r="R94" t="n">
-        <v>7009041</v>
+        <v>7008940</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10972,32 +10972,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132934657</v>
+        <v>132934711</v>
       </c>
       <c r="B95" t="n">
-        <v>80399</v>
+        <v>92202</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229497</v>
+        <v>65</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>521311</v>
+        <v>521269</v>
       </c>
       <c r="R95" t="n">
-        <v>7009049</v>
+        <v>7008900</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11069,42 +11069,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132934508</v>
+        <v>132934723</v>
       </c>
       <c r="B96" t="n">
-        <v>91920</v>
+        <v>93216</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>521332</v>
+        <v>521262</v>
       </c>
       <c r="R96" t="n">
         <v>7009041</v>
@@ -11134,12 +11134,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11166,10 +11166,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132934711</v>
+        <v>132934668</v>
       </c>
       <c r="B97" t="n">
-        <v>92194</v>
+        <v>99140</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11177,21 +11177,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11201,10 +11201,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>521269</v>
+        <v>521460</v>
       </c>
       <c r="R97" t="n">
-        <v>7008900</v>
+        <v>7008862</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11237,6 +11237,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11263,32 +11268,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132934668</v>
+        <v>132934657</v>
       </c>
       <c r="B98" t="n">
-        <v>99132</v>
+        <v>80399</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11298,10 +11303,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>521460</v>
+        <v>521311</v>
       </c>
       <c r="R98" t="n">
-        <v>7008862</v>
+        <v>7009049</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11328,17 +11333,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11365,32 +11365,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132934685</v>
+        <v>132934621</v>
       </c>
       <c r="B99" t="n">
-        <v>92094</v>
+        <v>79092</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>521278</v>
+        <v>521284</v>
       </c>
       <c r="R99" t="n">
-        <v>7008985</v>
+        <v>7008883</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11462,32 +11462,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132934603</v>
+        <v>132934580</v>
       </c>
       <c r="B100" t="n">
-        <v>80343</v>
+        <v>79924</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6456</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>521339</v>
+        <v>521256</v>
       </c>
       <c r="R100" t="n">
-        <v>7009060</v>
+        <v>7008979</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11527,12 +11527,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11559,10 +11559,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132934505</v>
+        <v>132934520</v>
       </c>
       <c r="B101" t="n">
-        <v>97372</v>
+        <v>79092</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11570,21 +11570,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11594,10 +11594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>521304</v>
+        <v>521367</v>
       </c>
       <c r="R101" t="n">
-        <v>7009055</v>
+        <v>7008928</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11656,32 +11656,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132934621</v>
+        <v>132934603</v>
       </c>
       <c r="B102" t="n">
-        <v>79092</v>
+        <v>80343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11691,10 +11691,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>521284</v>
+        <v>521339</v>
       </c>
       <c r="R102" t="n">
-        <v>7008883</v>
+        <v>7009060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11721,12 +11721,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11753,32 +11753,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132934580</v>
+        <v>132934685</v>
       </c>
       <c r="B103" t="n">
-        <v>79924</v>
+        <v>92102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>521256</v>
+        <v>521278</v>
       </c>
       <c r="R103" t="n">
-        <v>7008979</v>
+        <v>7008985</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11850,10 +11850,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132934520</v>
+        <v>132934505</v>
       </c>
       <c r="B104" t="n">
-        <v>79092</v>
+        <v>97380</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11861,21 +11861,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11885,10 +11885,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>521367</v>
+        <v>521304</v>
       </c>
       <c r="R104" t="n">
-        <v>7008928</v>
+        <v>7009055</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11947,32 +11947,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132934669</v>
+        <v>132934643</v>
       </c>
       <c r="B105" t="n">
-        <v>99132</v>
+        <v>80439</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>521481</v>
+        <v>521368</v>
       </c>
       <c r="R105" t="n">
-        <v>7008912</v>
+        <v>7009037</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,11 +12018,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12049,32 +12044,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132934643</v>
+        <v>132934669</v>
       </c>
       <c r="B106" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12084,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>521368</v>
+        <v>521481</v>
       </c>
       <c r="R106" t="n">
-        <v>7009037</v>
+        <v>7008912</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12120,6 +12115,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12243,10 +12243,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132934715</v>
+        <v>132934637</v>
       </c>
       <c r="B108" t="n">
-        <v>79000</v>
+        <v>80439</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12254,21 +12254,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>521370</v>
+        <v>521330</v>
       </c>
       <c r="R108" t="n">
-        <v>7008865</v>
+        <v>7009056</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12308,12 +12308,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12340,10 +12345,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132934637</v>
+        <v>132934715</v>
       </c>
       <c r="B109" t="n">
-        <v>80439</v>
+        <v>79000</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12351,21 +12356,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12375,10 +12380,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>521330</v>
+        <v>521370</v>
       </c>
       <c r="R109" t="n">
-        <v>7009056</v>
+        <v>7008865</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12405,17 +12410,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12445,7 +12445,7 @@
         <v>132934712</v>
       </c>
       <c r="B110" t="n">
-        <v>92194</v>
+        <v>92202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12738,32 +12738,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132934689</v>
+        <v>132934732</v>
       </c>
       <c r="B113" t="n">
-        <v>92094</v>
+        <v>78737</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12773,10 +12773,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>521289</v>
+        <v>521236</v>
       </c>
       <c r="R113" t="n">
-        <v>7009060</v>
+        <v>7009004</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12803,12 +12803,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12835,10 +12835,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132934732</v>
+        <v>132934717</v>
       </c>
       <c r="B114" t="n">
-        <v>78737</v>
+        <v>79000</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12846,21 +12846,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>521236</v>
+        <v>521268</v>
       </c>
       <c r="R114" t="n">
-        <v>7009004</v>
+        <v>7008957</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12932,10 +12932,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132934717</v>
+        <v>132934584</v>
       </c>
       <c r="B115" t="n">
-        <v>79000</v>
+        <v>91928</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12943,21 +12943,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12967,10 +12967,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>521268</v>
+        <v>521471</v>
       </c>
       <c r="R115" t="n">
-        <v>7008957</v>
+        <v>7008946</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13029,32 +13029,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132934584</v>
+        <v>132934689</v>
       </c>
       <c r="B116" t="n">
-        <v>91920</v>
+        <v>92102</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13064,10 +13064,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>521471</v>
+        <v>521289</v>
       </c>
       <c r="R116" t="n">
-        <v>7008946</v>
+        <v>7009060</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13094,12 +13094,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13223,10 +13223,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132934539</v>
+        <v>132934697</v>
       </c>
       <c r="B118" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13234,34 +13234,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>521382</v>
+        <v>521311</v>
       </c>
       <c r="R118" t="n">
-        <v>7008892</v>
+        <v>7008958</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13288,12 +13288,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13320,32 +13320,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132934697</v>
+        <v>132934658</v>
       </c>
       <c r="B119" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>521311</v>
+        <v>521301</v>
       </c>
       <c r="R119" t="n">
-        <v>7008958</v>
+        <v>7009055</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13385,12 +13385,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13417,45 +13417,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132934658</v>
+        <v>132934539</v>
       </c>
       <c r="B120" t="n">
-        <v>80399</v>
+        <v>79091</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>521301</v>
+        <v>521382</v>
       </c>
       <c r="R120" t="n">
-        <v>7009055</v>
+        <v>7008892</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132934695</v>
+        <v>132934644</v>
       </c>
       <c r="B121" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13525,21 +13525,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>521390</v>
+        <v>521346</v>
       </c>
       <c r="R121" t="n">
-        <v>7009009</v>
+        <v>7009052</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13579,12 +13579,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13611,10 +13611,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>132934644</v>
+        <v>132934695</v>
       </c>
       <c r="B122" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13622,21 +13622,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>521346</v>
+        <v>521390</v>
       </c>
       <c r="R122" t="n">
-        <v>7009052</v>
+        <v>7009009</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13676,12 +13676,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13708,10 +13708,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>132934622</v>
+        <v>132934731</v>
       </c>
       <c r="B123" t="n">
-        <v>79092</v>
+        <v>78341</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13719,21 +13719,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13743,10 +13743,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>521453</v>
+        <v>521235</v>
       </c>
       <c r="R123" t="n">
-        <v>7008881</v>
+        <v>7009006</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13805,32 +13805,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>132934720</v>
+        <v>132934622</v>
       </c>
       <c r="B124" t="n">
-        <v>93208</v>
+        <v>79092</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>521341</v>
+        <v>521453</v>
       </c>
       <c r="R124" t="n">
-        <v>7008936</v>
+        <v>7008881</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13902,32 +13902,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132934731</v>
+        <v>132934720</v>
       </c>
       <c r="B125" t="n">
-        <v>78341</v>
+        <v>93216</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13937,10 +13937,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>521235</v>
+        <v>521341</v>
       </c>
       <c r="R125" t="n">
-        <v>7009006</v>
+        <v>7008936</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14193,32 +14193,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>132934687</v>
+        <v>132934659</v>
       </c>
       <c r="B128" t="n">
-        <v>92094</v>
+        <v>80399</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>229497</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>521353</v>
+        <v>521290</v>
       </c>
       <c r="R128" t="n">
-        <v>7008975</v>
+        <v>7009063</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14290,32 +14290,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132934722</v>
+        <v>132934581</v>
       </c>
       <c r="B129" t="n">
-        <v>93208</v>
+        <v>79924</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14325,10 +14325,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>521256</v>
+        <v>521230</v>
       </c>
       <c r="R129" t="n">
-        <v>7009005</v>
+        <v>7009003</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14581,32 +14581,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>132934659</v>
+        <v>132934687</v>
       </c>
       <c r="B132" t="n">
-        <v>80399</v>
+        <v>92102</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14616,10 +14616,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>521290</v>
+        <v>521353</v>
       </c>
       <c r="R132" t="n">
-        <v>7009063</v>
+        <v>7008975</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14678,32 +14678,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132934581</v>
+        <v>132934722</v>
       </c>
       <c r="B133" t="n">
-        <v>79924</v>
+        <v>93216</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14713,10 +14713,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>521230</v>
+        <v>521256</v>
       </c>
       <c r="R133" t="n">
-        <v>7009003</v>
+        <v>7009005</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14969,32 +14969,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132934686</v>
+        <v>132934714</v>
       </c>
       <c r="B136" t="n">
-        <v>92094</v>
+        <v>79000</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15004,10 +15004,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>521364</v>
+        <v>521381</v>
       </c>
       <c r="R136" t="n">
-        <v>7008948</v>
+        <v>7008904</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15066,32 +15066,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132934714</v>
+        <v>132934686</v>
       </c>
       <c r="B137" t="n">
-        <v>79000</v>
+        <v>92102</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15101,10 +15101,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>521381</v>
+        <v>521364</v>
       </c>
       <c r="R137" t="n">
-        <v>7008904</v>
+        <v>7008948</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15131,12 +15131,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15551,32 +15551,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132934561</v>
+        <v>132934648</v>
       </c>
       <c r="B142" t="n">
-        <v>91842</v>
+        <v>80306</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3242</v>
+        <v>385</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>521263</v>
+        <v>521468</v>
       </c>
       <c r="R142" t="n">
-        <v>7008978</v>
+        <v>7008870</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15630,6 +15630,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15648,45 +15649,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132934648</v>
+        <v>132934509</v>
       </c>
       <c r="B143" t="n">
-        <v>80306</v>
+        <v>91928</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>385</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>AA, Jmt</t>
+          <t>AB, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>521468</v>
+        <v>521329</v>
       </c>
       <c r="R143" t="n">
-        <v>7008870</v>
+        <v>7009049</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15713,12 +15714,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15727,7 +15728,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15746,10 +15746,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132934509</v>
+        <v>132934561</v>
       </c>
       <c r="B144" t="n">
-        <v>91920</v>
+        <v>91850</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15757,34 +15757,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>3242</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>AB, Jmt</t>
+          <t>AA, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>521329</v>
+        <v>521263</v>
       </c>
       <c r="R144" t="n">
-        <v>7009049</v>
+        <v>7008978</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15811,12 +15811,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -16239,7 +16239,7 @@
         <v>132811909</v>
       </c>
       <c r="B149" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -16239,7 +16239,7 @@
         <v>132811909</v>
       </c>
       <c r="B149" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 62432-2025 artfynd.xlsx
+++ b/artfynd/A 62432-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY162"/>
+  <dimension ref="A1:AZ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934563</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934711</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934712</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934713</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934715</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934716</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934717</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934718</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934719</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1944,6 +2009,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934648</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934512</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2255,6 +2335,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840099</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2390,6 +2475,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811905</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,6 +2610,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811907</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2734,6 +2834,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840108</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2831,6 +2936,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934508</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2928,6 +3038,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934509</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3025,6 +3140,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934584</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3165,6 +3285,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840122</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934553</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3359,6 +3489,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934682</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3456,6 +3591,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934683</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3553,6 +3693,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934685</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3650,6 +3795,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934686</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3747,6 +3897,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934687</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3844,6 +3999,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934688</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3941,6 +4101,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934689</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4063,6 +4228,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840092</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4160,6 +4330,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934617</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4272,6 +4447,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811937</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4384,6 +4564,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811939</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4481,6 +4666,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934561</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4578,6 +4768,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934720</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4675,6 +4870,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934721</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4772,6 +4972,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934722</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4869,6 +5074,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934723</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5000,6 +5210,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811955</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5126,6 +5341,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811957</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5252,6 +5472,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811959</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5378,6 +5603,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811960</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5509,6 +5739,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811962</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5635,6 +5870,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811965</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5766,6 +6006,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811966</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5892,6 +6137,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811968</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6018,6 +6268,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811970</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6149,6 +6404,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811972</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6275,6 +6535,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811973</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6397,6 +6662,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840091</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6504,6 +6774,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840098</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6611,6 +6886,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840102</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6718,6 +6998,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840106</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6825,6 +7110,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840112</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6932,6 +7222,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840124</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7034,6 +7329,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934556</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7131,6 +7431,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934692</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7228,6 +7533,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934694</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7325,6 +7635,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934695</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7422,6 +7737,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934696</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7519,6 +7839,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934697</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7616,6 +7941,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934698</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7713,6 +8043,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934699</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7810,6 +8145,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934700</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7907,6 +8247,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934705</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8004,6 +8349,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934706</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8101,6 +8451,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934707</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8198,6 +8553,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934708</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8305,6 +8665,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840127</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8402,6 +8767,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934732</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8509,6 +8879,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840103</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8616,6 +8991,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840110</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8747,6 +9127,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811941</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8844,6 +9229,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934537</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8941,6 +9331,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934538</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9038,6 +9433,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934539</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9135,6 +9535,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934540</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9232,6 +9637,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934661</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9339,6 +9749,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840087</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9436,6 +9851,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934568</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9533,6 +9953,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934603</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9668,6 +10093,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811932</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9775,6 +10205,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840095</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9882,6 +10317,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840096</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9979,6 +10419,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934632</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10076,6 +10521,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934635</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10173,6 +10623,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934636</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10275,6 +10730,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934637</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10372,6 +10832,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934638</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10469,6 +10934,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934639</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10566,6 +11036,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934643</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10663,6 +11138,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934644</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10765,6 +11245,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934645</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10871,6 +11356,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811924</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10977,6 +11467,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811926</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11088,6 +11583,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811927</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11185,6 +11685,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934731</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11324,6 +11829,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811909</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11443,6 +11953,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811914</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11561,6 +12076,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811912</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11672,6 +12192,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811934</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11788,6 +12313,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811936</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11916,6 +12446,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811943</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12044,6 +12579,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811944</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12172,6 +12712,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811946</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12300,6 +12845,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811948</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12428,6 +12978,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811949</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12556,6 +13111,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811951</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12658,6 +13218,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934668</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12760,6 +13325,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934669</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12867,6 +13437,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811919</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12983,6 +13558,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811916</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13094,6 +13674,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811984</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13205,6 +13790,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811986</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13321,6 +13911,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811988</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13428,6 +14023,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840101</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13535,6 +14135,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840113</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13642,6 +14247,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840111</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13753,6 +14363,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811952</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13859,6 +14474,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811976</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13965,6 +14585,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811977</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14071,6 +14696,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811979</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14177,6 +14807,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811981</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14283,6 +14918,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811983</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14414,6 +15054,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811929</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14545,6 +15190,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811931</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14652,6 +15302,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840088</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14759,6 +15414,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840089</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14866,6 +15526,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840117</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14973,6 +15638,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840123</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15070,6 +15740,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934518</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15167,6 +15842,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934519</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15264,6 +15944,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934520</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15361,6 +16046,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934621</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15458,6 +16148,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934622</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15555,6 +16250,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934623</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15652,6 +16352,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934624</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15779,6 +16484,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840090</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15886,6 +16596,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840097</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15993,6 +16708,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840116</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16090,6 +16810,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934536</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16187,6 +16912,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934649</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16284,6 +17014,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934650</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16381,6 +17116,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934651</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16483,6 +17223,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934652</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16580,6 +17325,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934653</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16677,6 +17427,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934654</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16774,6 +17529,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934656</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16871,6 +17631,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934657</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16968,6 +17733,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934658</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17065,6 +17835,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934659</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17191,6 +17966,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811902</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17322,6 +18102,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132811903</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17429,6 +18214,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132840126</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17526,6 +18316,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934578</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17623,6 +18418,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934579</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17720,6 +18520,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934580</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17817,8 +18622,176 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132934581</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>